--- a/season/season-2324_csv.xlsx
+++ b/season/season-2324_csv.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="182">
   <si>
     <t>Giornata</t>
   </si>
@@ -112,6 +112,33 @@
     <t>25</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>2023-08-19</t>
   </si>
   <si>
@@ -316,6 +343,9 @@
     <t>2024-02-22</t>
   </si>
   <si>
+    <t>2024-02-28</t>
+  </si>
+  <si>
     <t>2024-01-26</t>
   </si>
   <si>
@@ -359,6 +389,111 @@
   </si>
   <si>
     <t>2024-02-18</t>
+  </si>
+  <si>
+    <t>2024-02-23</t>
+  </si>
+  <si>
+    <t>2024-02-24</t>
+  </si>
+  <si>
+    <t>2024-02-25</t>
+  </si>
+  <si>
+    <t>2024-02-26</t>
+  </si>
+  <si>
+    <t>2024-03-01</t>
+  </si>
+  <si>
+    <t>2024-03-02</t>
+  </si>
+  <si>
+    <t>2024-03-03</t>
+  </si>
+  <si>
+    <t>2024-03-04</t>
+  </si>
+  <si>
+    <t>2024-03-08</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>2024-03-10</t>
+  </si>
+  <si>
+    <t>2024-03-11</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
+    <t>2024-03-15</t>
+  </si>
+  <si>
+    <t>2024-03-16</t>
+  </si>
+  <si>
+    <t>2024-03-17</t>
+  </si>
+  <si>
+    <t>2024-03-30</t>
+  </si>
+  <si>
+    <t>2024-04-01</t>
+  </si>
+  <si>
+    <t>2024-04-05</t>
+  </si>
+  <si>
+    <t>2024-04-06</t>
+  </si>
+  <si>
+    <t>2024-04-07</t>
+  </si>
+  <si>
+    <t>2024-04-08</t>
+  </si>
+  <si>
+    <t>2024-04-12</t>
+  </si>
+  <si>
+    <t>2024-04-13</t>
+  </si>
+  <si>
+    <t>2024-04-14</t>
+  </si>
+  <si>
+    <t>2024-04-15</t>
+  </si>
+  <si>
+    <t>2024-04-25</t>
+  </si>
+  <si>
+    <t>2024-04-19</t>
+  </si>
+  <si>
+    <t>2024-04-20</t>
+  </si>
+  <si>
+    <t>2024-04-21</t>
+  </si>
+  <si>
+    <t>2024-04-22</t>
+  </si>
+  <si>
+    <t>2024-04-26</t>
+  </si>
+  <si>
+    <t>2024-04-27</t>
+  </si>
+  <si>
+    <t>2024-04-28</t>
+  </si>
+  <si>
+    <t>2024-04-29</t>
   </si>
   <si>
     <t>Empoli</t>
@@ -782,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -813,22 +948,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -836,13 +971,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -851,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -859,13 +994,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -874,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -882,22 +1017,22 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -905,13 +1040,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -920,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -928,22 +1063,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -951,13 +1086,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -966,7 +1101,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -974,22 +1109,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -997,22 +1132,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1020,22 +1155,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1043,13 +1178,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1058,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1066,22 +1201,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1089,13 +1224,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1104,7 +1239,7 @@
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1112,13 +1247,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1127,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1135,13 +1270,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1150,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1158,13 +1293,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -1173,7 +1308,7 @@
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1181,22 +1316,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1204,22 +1339,22 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1227,13 +1362,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -1242,7 +1377,7 @@
         <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1250,22 +1385,22 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1273,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1288,7 +1423,7 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1296,13 +1431,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -1311,7 +1446,7 @@
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1319,13 +1454,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1334,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1342,22 +1477,22 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1365,22 +1500,22 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1388,13 +1523,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -1403,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1411,22 +1546,22 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1434,22 +1569,22 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1457,22 +1592,22 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1480,22 +1615,22 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1503,13 +1638,13 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -1518,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1526,13 +1661,13 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
@@ -1541,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1549,13 +1684,13 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -1564,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1572,22 +1707,22 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1595,13 +1730,13 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -1610,7 +1745,7 @@
         <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1618,13 +1753,13 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -1633,7 +1768,7 @@
         <v>7</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1641,13 +1776,13 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -1656,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1664,22 +1799,22 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E39" t="s">
         <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1687,22 +1822,22 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1710,22 +1845,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F41" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1733,13 +1868,13 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -1748,7 +1883,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1756,22 +1891,22 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1779,22 +1914,22 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1802,13 +1937,13 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -1817,7 +1952,7 @@
         <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1825,13 +1960,13 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -1840,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1848,22 +1983,22 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E47" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1871,22 +2006,22 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1894,22 +2029,22 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F49" t="s">
         <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1917,22 +2052,22 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E50" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F50" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1940,13 +2075,13 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -1955,7 +2090,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1963,22 +2098,22 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1986,13 +2121,13 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -2001,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2009,22 +2144,22 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G54" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2032,22 +2167,22 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E55" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
       </c>
       <c r="G55" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2055,13 +2190,13 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -2070,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2078,22 +2213,22 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G57" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2101,13 +2236,13 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -2116,7 +2251,7 @@
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2124,13 +2259,13 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -2139,7 +2274,7 @@
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2147,22 +2282,22 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E60" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F60" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G60" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2170,13 +2305,13 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -2185,7 +2320,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2193,22 +2328,22 @@
         <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F62" t="s">
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2216,22 +2351,22 @@
         <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G63" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2239,22 +2374,22 @@
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
       </c>
       <c r="G64" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2262,22 +2397,22 @@
         <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D65" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G65" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2285,13 +2420,13 @@
         <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D66" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -2300,7 +2435,7 @@
         <v>8</v>
       </c>
       <c r="G66" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2308,22 +2443,22 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E67" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F67" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G67" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2331,22 +2466,22 @@
         <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D68" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G68" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2354,22 +2489,22 @@
         <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C69" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D69" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
       </c>
       <c r="G69" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2377,22 +2512,22 @@
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D70" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F70" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G70" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2400,22 +2535,22 @@
         <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G71" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2423,22 +2558,22 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D72" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E72" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F72" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G72" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2446,13 +2581,13 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -2461,7 +2596,7 @@
         <v>7</v>
       </c>
       <c r="G73" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2469,13 +2604,13 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -2484,7 +2619,7 @@
         <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2492,22 +2627,22 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D75" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G75" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2515,22 +2650,22 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C76" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E76" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2538,22 +2673,22 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G77" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2561,13 +2696,13 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -2576,7 +2711,7 @@
         <v>7</v>
       </c>
       <c r="G78" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2584,13 +2719,13 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -2599,7 +2734,7 @@
         <v>8</v>
       </c>
       <c r="G79" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2607,13 +2742,13 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D80" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
         <v>7</v>
@@ -2622,7 +2757,7 @@
         <v>10</v>
       </c>
       <c r="G80" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2630,13 +2765,13 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C81" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E81" t="s">
         <v>7</v>
@@ -2645,7 +2780,7 @@
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2653,13 +2788,13 @@
         <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E82" t="s">
         <v>7</v>
@@ -2668,7 +2803,7 @@
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2676,22 +2811,22 @@
         <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D83" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E83" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2699,22 +2834,22 @@
         <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E84" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2722,22 +2857,22 @@
         <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E85" t="s">
         <v>7</v>
       </c>
       <c r="F85" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2745,13 +2880,13 @@
         <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C86" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D86" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -2760,7 +2895,7 @@
         <v>7</v>
       </c>
       <c r="G86" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2768,13 +2903,13 @@
         <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -2783,7 +2918,7 @@
         <v>8</v>
       </c>
       <c r="G87" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2791,22 +2926,22 @@
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C88" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D88" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G88" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2814,22 +2949,22 @@
         <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E89" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F89" t="s">
         <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2837,13 +2972,13 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D90" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
         <v>7</v>
@@ -2852,7 +2987,7 @@
         <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2860,22 +2995,22 @@
         <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C91" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D91" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E91" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2883,22 +3018,22 @@
         <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
       </c>
       <c r="F92" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G92" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2906,13 +3041,13 @@
         <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C93" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D93" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -2921,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2929,22 +3064,22 @@
         <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C94" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D94" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E94" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F94" t="s">
         <v>7</v>
       </c>
       <c r="G94" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2952,22 +3087,22 @@
         <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
       </c>
       <c r="F95" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G95" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2975,13 +3110,13 @@
         <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D96" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -2990,7 +3125,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2998,13 +3133,13 @@
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D97" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -3013,7 +3148,7 @@
         <v>7</v>
       </c>
       <c r="G97" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3021,22 +3156,22 @@
         <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
       </c>
       <c r="F98" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G98" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3044,13 +3179,13 @@
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3059,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3067,22 +3202,22 @@
         <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E100" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F100" t="s">
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3090,22 +3225,22 @@
         <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C101" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E101" t="s">
         <v>7</v>
       </c>
       <c r="F101" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G101" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3113,22 +3248,22 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E102" t="s">
         <v>7</v>
       </c>
       <c r="F102" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G102" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3136,22 +3271,22 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C103" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D103" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E103" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
       </c>
       <c r="G103" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3159,13 +3294,13 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C104" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D104" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E104" t="s">
         <v>7</v>
@@ -3174,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3182,22 +3317,22 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C105" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E105" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F105" t="s">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3205,13 +3340,13 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C106" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D106" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E106" t="s">
         <v>7</v>
@@ -3220,7 +3355,7 @@
         <v>9</v>
       </c>
       <c r="G106" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3228,13 +3363,13 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D107" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3243,7 +3378,7 @@
         <v>7</v>
       </c>
       <c r="G107" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3251,13 +3386,13 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D108" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3266,7 +3401,7 @@
         <v>7</v>
       </c>
       <c r="G108" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3274,22 +3409,22 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C109" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D109" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E109" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F109" t="s">
         <v>7</v>
       </c>
       <c r="G109" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3297,13 +3432,13 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C110" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D110" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3312,7 +3447,7 @@
         <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3320,13 +3455,13 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D111" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3335,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="G111" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3343,13 +3478,13 @@
         <v>18</v>
       </c>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3358,7 +3493,7 @@
         <v>8</v>
       </c>
       <c r="G112" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3366,22 +3501,22 @@
         <v>18</v>
       </c>
       <c r="B113" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C113" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E113" t="s">
         <v>7</v>
       </c>
       <c r="F113" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G113" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3389,13 +3524,13 @@
         <v>18</v>
       </c>
       <c r="B114" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C114" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3404,7 +3539,7 @@
         <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3412,13 +3547,13 @@
         <v>18</v>
       </c>
       <c r="B115" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D115" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3427,7 +3562,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3435,13 +3570,13 @@
         <v>18</v>
       </c>
       <c r="B116" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D116" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E116" t="s">
         <v>7</v>
@@ -3450,7 +3585,7 @@
         <v>7</v>
       </c>
       <c r="G116" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3458,22 +3593,22 @@
         <v>18</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C117" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D117" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E117" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F117" t="s">
         <v>7</v>
       </c>
       <c r="G117" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3481,13 +3616,13 @@
         <v>18</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C118" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D118" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3496,7 +3631,7 @@
         <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3504,13 +3639,13 @@
         <v>18</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C119" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D119" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E119" t="s">
         <v>7</v>
@@ -3519,7 +3654,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3527,22 +3662,22 @@
         <v>18</v>
       </c>
       <c r="B120" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C120" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E120" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F120" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G120" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3550,22 +3685,22 @@
         <v>18</v>
       </c>
       <c r="B121" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C121" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D121" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
       </c>
       <c r="F121" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G121" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3573,13 +3708,13 @@
         <v>19</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C122" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D122" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -3588,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3596,13 +3731,13 @@
         <v>19</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C123" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D123" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E123" t="s">
         <v>7</v>
@@ -3611,7 +3746,7 @@
         <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3619,22 +3754,22 @@
         <v>19</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C124" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D124" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E124" t="s">
         <v>7</v>
       </c>
       <c r="F124" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G124" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3642,13 +3777,13 @@
         <v>19</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D125" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E125" t="s">
         <v>7</v>
@@ -3657,7 +3792,7 @@
         <v>7</v>
       </c>
       <c r="G125" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3665,13 +3800,13 @@
         <v>19</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C126" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D126" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -3680,7 +3815,7 @@
         <v>10</v>
       </c>
       <c r="G126" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3688,13 +3823,13 @@
         <v>19</v>
       </c>
       <c r="B127" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C127" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D127" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -3703,7 +3838,7 @@
         <v>7</v>
       </c>
       <c r="G127" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3711,13 +3846,13 @@
         <v>19</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C128" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D128" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -3726,7 +3861,7 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3734,13 +3869,13 @@
         <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C129" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D129" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E129" t="s">
         <v>7</v>
@@ -3749,7 +3884,7 @@
         <v>7</v>
       </c>
       <c r="G129" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3757,13 +3892,13 @@
         <v>19</v>
       </c>
       <c r="B130" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C130" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D130" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -3772,7 +3907,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3780,22 +3915,22 @@
         <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C131" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D131" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
       </c>
       <c r="F131" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G131" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3803,13 +3938,13 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C132" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E132" t="s">
         <v>7</v>
@@ -3818,7 +3953,7 @@
         <v>8</v>
       </c>
       <c r="G132" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3826,13 +3961,13 @@
         <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C133" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D133" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E133" t="s">
         <v>7</v>
@@ -3841,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="G133" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3849,22 +3984,22 @@
         <v>20</v>
       </c>
       <c r="B134" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C134" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D134" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E134" t="s">
         <v>7</v>
       </c>
       <c r="F134" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G134" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3872,13 +4007,13 @@
         <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C135" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D135" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -3887,7 +4022,7 @@
         <v>7</v>
       </c>
       <c r="G135" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3895,13 +4030,13 @@
         <v>20</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C136" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D136" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E136" t="s">
         <v>7</v>
@@ -3910,7 +4045,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3918,22 +4053,22 @@
         <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C137" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D137" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
       </c>
       <c r="F137" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G137" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3941,13 +4076,13 @@
         <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C138" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D138" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -3956,7 +4091,7 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3964,13 +4099,13 @@
         <v>20</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C139" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E139" t="s">
         <v>7</v>
@@ -3979,7 +4114,7 @@
         <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3987,22 +4122,22 @@
         <v>20</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C140" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D140" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E140" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F140" t="s">
         <v>9</v>
       </c>
       <c r="G140" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4010,22 +4145,22 @@
         <v>20</v>
       </c>
       <c r="B141" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C141" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D141" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G141" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4033,22 +4168,22 @@
         <v>21</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C142" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D142" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E142" t="s">
         <v>7</v>
       </c>
       <c r="F142" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G142" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4056,13 +4191,13 @@
         <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D143" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E143" t="s">
         <v>7</v>
@@ -4071,7 +4206,7 @@
         <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4079,13 +4214,13 @@
         <v>21</v>
       </c>
       <c r="B144" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D144" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -4094,7 +4229,7 @@
         <v>8</v>
       </c>
       <c r="G144" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4102,22 +4237,22 @@
         <v>21</v>
       </c>
       <c r="B145" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G145" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4125,22 +4260,22 @@
         <v>21</v>
       </c>
       <c r="B146" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C146" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D146" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E146" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F146" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G146" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4148,22 +4283,22 @@
         <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C147" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D147" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E147" t="s">
         <v>7</v>
       </c>
       <c r="F147" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G147" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4171,13 +4306,13 @@
         <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C148" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D148" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E148" t="s">
         <v>7</v>
@@ -4186,7 +4321,7 @@
         <v>8</v>
       </c>
       <c r="G148" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4194,13 +4329,13 @@
         <v>21</v>
       </c>
       <c r="B149" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C149" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D149" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E149" t="s">
         <v>7</v>
@@ -4209,7 +4344,7 @@
         <v>7</v>
       </c>
       <c r="G149" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4217,13 +4352,13 @@
         <v>21</v>
       </c>
       <c r="B150" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C150" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D150" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E150" t="s">
         <v>7</v>
@@ -4232,7 +4367,7 @@
         <v>7</v>
       </c>
       <c r="G150" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4240,13 +4375,13 @@
         <v>21</v>
       </c>
       <c r="B151" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C151" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D151" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4255,7 +4390,7 @@
         <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4263,13 +4398,13 @@
         <v>22</v>
       </c>
       <c r="B152" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C152" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D152" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E152" t="s">
         <v>7</v>
@@ -4278,7 +4413,7 @@
         <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4286,13 +4421,13 @@
         <v>22</v>
       </c>
       <c r="B153" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C153" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D153" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4301,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="G153" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4309,13 +4444,13 @@
         <v>22</v>
       </c>
       <c r="B154" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C154" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D154" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4324,7 +4459,7 @@
         <v>7</v>
       </c>
       <c r="G154" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4332,22 +4467,22 @@
         <v>22</v>
       </c>
       <c r="B155" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C155" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D155" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E155" t="s">
         <v>7</v>
       </c>
       <c r="F155" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G155" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4355,22 +4490,22 @@
         <v>22</v>
       </c>
       <c r="B156" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C156" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D156" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G156" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4378,22 +4513,22 @@
         <v>22</v>
       </c>
       <c r="B157" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C157" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D157" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E157" t="s">
         <v>7</v>
       </c>
       <c r="F157" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G157" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4401,13 +4536,13 @@
         <v>22</v>
       </c>
       <c r="B158" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D158" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4416,7 +4551,7 @@
         <v>8</v>
       </c>
       <c r="G158" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4424,22 +4559,22 @@
         <v>22</v>
       </c>
       <c r="B159" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C159" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D159" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
       </c>
       <c r="F159" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G159" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4447,22 +4582,22 @@
         <v>22</v>
       </c>
       <c r="B160" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C160" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D160" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F160" t="s">
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4470,13 +4605,13 @@
         <v>22</v>
       </c>
       <c r="B161" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D161" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -4485,7 +4620,7 @@
         <v>7</v>
       </c>
       <c r="G161" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4493,22 +4628,22 @@
         <v>23</v>
       </c>
       <c r="B162" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C162" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D162" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E162" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4516,13 +4651,13 @@
         <v>23</v>
       </c>
       <c r="B163" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D163" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E163" t="s">
         <v>7</v>
@@ -4531,7 +4666,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4539,22 +4674,22 @@
         <v>23</v>
       </c>
       <c r="B164" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D164" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E164" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F164" t="s">
         <v>7</v>
       </c>
       <c r="G164" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4562,13 +4697,13 @@
         <v>23</v>
       </c>
       <c r="B165" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D165" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4577,7 +4712,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4585,13 +4720,13 @@
         <v>23</v>
       </c>
       <c r="B166" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C166" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D166" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E166" t="s">
         <v>7</v>
@@ -4600,7 +4735,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4608,22 +4743,22 @@
         <v>23</v>
       </c>
       <c r="B167" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C167" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E167" t="s">
         <v>7</v>
       </c>
       <c r="F167" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G167" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4631,13 +4766,13 @@
         <v>23</v>
       </c>
       <c r="B168" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C168" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D168" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E168" t="s">
         <v>7</v>
@@ -4646,7 +4781,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4654,22 +4789,22 @@
         <v>23</v>
       </c>
       <c r="B169" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C169" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D169" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
       </c>
       <c r="F169" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G169" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4677,22 +4812,22 @@
         <v>23</v>
       </c>
       <c r="B170" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C170" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D170" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
       </c>
       <c r="F170" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G170" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4700,22 +4835,22 @@
         <v>23</v>
       </c>
       <c r="B171" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D171" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
       </c>
       <c r="F171" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G171" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4723,22 +4858,22 @@
         <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C172" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D172" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E172" t="s">
         <v>7</v>
       </c>
       <c r="F172" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G172" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4746,22 +4881,22 @@
         <v>24</v>
       </c>
       <c r="B173" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D173" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E173" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F173" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G173" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4769,13 +4904,13 @@
         <v>24</v>
       </c>
       <c r="B174" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D174" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E174" t="s">
         <v>7</v>
@@ -4784,7 +4919,7 @@
         <v>7</v>
       </c>
       <c r="G174" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4792,13 +4927,13 @@
         <v>24</v>
       </c>
       <c r="B175" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
@@ -4807,7 +4942,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4815,22 +4950,22 @@
         <v>24</v>
       </c>
       <c r="B176" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C176" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D176" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E176" t="s">
         <v>7</v>
       </c>
       <c r="F176" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G176" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4838,22 +4973,22 @@
         <v>24</v>
       </c>
       <c r="B177" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C177" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D177" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E177" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F177" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G177" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4861,22 +4996,22 @@
         <v>24</v>
       </c>
       <c r="B178" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D178" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
       </c>
       <c r="F178" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G178" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4884,22 +5019,22 @@
         <v>24</v>
       </c>
       <c r="B179" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D179" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E179" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F179" t="s">
         <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4907,22 +5042,22 @@
         <v>24</v>
       </c>
       <c r="B180" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C180" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D180" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E180" t="s">
         <v>7</v>
       </c>
       <c r="F180" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G180" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4930,22 +5065,22 @@
         <v>24</v>
       </c>
       <c r="B181" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C181" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E181" t="s">
         <v>7</v>
       </c>
       <c r="F181" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G181" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4953,13 +5088,13 @@
         <v>25</v>
       </c>
       <c r="B182" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D182" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E182" t="s">
         <v>7</v>
@@ -4968,7 +5103,7 @@
         <v>7</v>
       </c>
       <c r="G182" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4976,13 +5111,13 @@
         <v>25</v>
       </c>
       <c r="B183" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C183" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D183" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -4991,7 +5126,7 @@
         <v>7</v>
       </c>
       <c r="G183" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4999,13 +5134,13 @@
         <v>25</v>
       </c>
       <c r="B184" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C184" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D184" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -5014,7 +5149,7 @@
         <v>9</v>
       </c>
       <c r="G184" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5022,13 +5157,13 @@
         <v>25</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C185" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D185" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E185" t="s">
         <v>7</v>
@@ -5037,7 +5172,7 @@
         <v>7</v>
       </c>
       <c r="G185" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5045,22 +5180,22 @@
         <v>25</v>
       </c>
       <c r="B186" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C186" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="D186" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E186" t="s">
         <v>7</v>
       </c>
       <c r="F186" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G186" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5068,22 +5203,22 @@
         <v>25</v>
       </c>
       <c r="B187" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C187" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D187" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E187" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F187" t="s">
         <v>9</v>
       </c>
       <c r="G187" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5091,22 +5226,22 @@
         <v>25</v>
       </c>
       <c r="B188" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C188" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D188" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
       </c>
       <c r="F188" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G188" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5114,13 +5249,13 @@
         <v>25</v>
       </c>
       <c r="B189" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D189" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E189" t="s">
         <v>7</v>
@@ -5129,7 +5264,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5137,13 +5272,13 @@
         <v>25</v>
       </c>
       <c r="B190" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D190" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E190" t="s">
         <v>7</v>
@@ -5152,7 +5287,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5160,13 +5295,13 @@
         <v>25</v>
       </c>
       <c r="B191" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D191" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E191" t="s">
         <v>7</v>
@@ -5175,7 +5310,7 @@
         <v>7</v>
       </c>
       <c r="G191" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5183,22 +5318,22 @@
         <v>26</v>
       </c>
       <c r="B192" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C192" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="E192" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F192" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G192" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5206,13 +5341,13 @@
         <v>26</v>
       </c>
       <c r="B193" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C193" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D193" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5221,7 +5356,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5229,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="B194" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C194" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D194" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5244,7 +5379,7 @@
         <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5252,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="B195" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C195" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D195" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="E195" t="s">
         <v>7</v>
@@ -5267,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="G195" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5275,22 +5410,22 @@
         <v>26</v>
       </c>
       <c r="B196" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C196" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D196" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E196" t="s">
         <v>7</v>
       </c>
       <c r="F196" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G196" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5298,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="B197" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C197" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5313,7 +5448,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5321,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="B198" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C198" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5336,7 +5471,7 @@
         <v>8</v>
       </c>
       <c r="G198" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5344,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="B199" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C199" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="D199" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
@@ -5359,7 +5494,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5367,22 +5502,22 @@
         <v>26</v>
       </c>
       <c r="B200" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C200" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D200" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E200" t="s">
         <v>11</v>
       </c>
       <c r="F200" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G200" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5390,22 +5525,22 @@
         <v>26</v>
       </c>
       <c r="B201" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C201" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D201" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
       </c>
       <c r="F201" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G201" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5413,13 +5548,13 @@
         <v>27</v>
       </c>
       <c r="B202" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C202" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5428,7 +5563,7 @@
         <v>7</v>
       </c>
       <c r="G202" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5436,13 +5571,13 @@
         <v>27</v>
       </c>
       <c r="B203" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C203" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D203" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5451,7 +5586,7 @@
         <v>9</v>
       </c>
       <c r="G203" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5459,13 +5594,13 @@
         <v>27</v>
       </c>
       <c r="B204" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C204" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="D204" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -5474,7 +5609,7 @@
         <v>7</v>
       </c>
       <c r="G204" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5482,22 +5617,22 @@
         <v>27</v>
       </c>
       <c r="B205" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C205" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="D205" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
       </c>
       <c r="F205" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G205" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5505,13 +5640,13 @@
         <v>27</v>
       </c>
       <c r="B206" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C206" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D206" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="E206" t="s">
         <v>7</v>
@@ -5520,7 +5655,7 @@
         <v>8</v>
       </c>
       <c r="G206" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5528,22 +5663,22 @@
         <v>27</v>
       </c>
       <c r="B207" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C207" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D207" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E207" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F207" t="s">
         <v>9</v>
       </c>
       <c r="G207" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5551,22 +5686,22 @@
         <v>27</v>
       </c>
       <c r="B208" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C208" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D208" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
       </c>
       <c r="F208" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G208" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5574,68 +5709,68 @@
         <v>27</v>
       </c>
       <c r="B209" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C209" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D209" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="E209" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F209" t="s">
         <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B210" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C210" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="D210" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="E210" t="s">
         <v>7</v>
       </c>
       <c r="F210" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G210" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B211" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C211" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="D211" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="E211" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F211" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G211" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5643,22 +5778,22 @@
         <v>28</v>
       </c>
       <c r="B212" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C212" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="E212" t="s">
         <v>7</v>
       </c>
       <c r="F212" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G212" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5666,22 +5801,22 @@
         <v>28</v>
       </c>
       <c r="B213" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C213" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="D213" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
       </c>
       <c r="F213" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="G213" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5689,22 +5824,22 @@
         <v>28</v>
       </c>
       <c r="B214" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C214" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="D214" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="E214" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F214" t="s">
         <v>7</v>
       </c>
       <c r="G214" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5712,22 +5847,22 @@
         <v>28</v>
       </c>
       <c r="B215" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C215" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="D215" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="E215" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F215" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5735,22 +5870,22 @@
         <v>28</v>
       </c>
       <c r="B216" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C216" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="D216" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="E216" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F216" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G216" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5758,22 +5893,22 @@
         <v>28</v>
       </c>
       <c r="B217" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C217" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D217" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="E217" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F217" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G217" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5781,22 +5916,22 @@
         <v>28</v>
       </c>
       <c r="B218" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C218" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D218" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="E218" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F218" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="G218" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5804,68 +5939,68 @@
         <v>28</v>
       </c>
       <c r="B219" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C219" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="D219" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="E219" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="F219" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="G219" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B220" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C220" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="E220" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="F220" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B221" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C221" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="D221" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="E221" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F221" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G221" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5873,22 +6008,22 @@
         <v>29</v>
       </c>
       <c r="B222" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C222" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="D222" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="E222" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="F222" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G222" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5896,22 +6031,22 @@
         <v>29</v>
       </c>
       <c r="B223" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="D223" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="E223" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="F223" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="G223" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5919,22 +6054,22 @@
         <v>29</v>
       </c>
       <c r="B224" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C224" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="D224" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E224" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="F224" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="G224" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5942,22 +6077,22 @@
         <v>29</v>
       </c>
       <c r="B225" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D225" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="E225" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="F225" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="G225" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5965,22 +6100,22 @@
         <v>29</v>
       </c>
       <c r="B226" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C226" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="D226" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="E226" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G226" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5988,22 +6123,22 @@
         <v>29</v>
       </c>
       <c r="B227" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C227" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="D227" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="E227" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="F227" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="G227" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6011,22 +6146,22 @@
         <v>29</v>
       </c>
       <c r="B228" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C228" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="D228" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="E228" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F228" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G228" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6034,68 +6169,68 @@
         <v>29</v>
       </c>
       <c r="B229" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C229" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="E229" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F229" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G229" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B230" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C230" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="D230" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="E230" t="s">
         <v>7</v>
       </c>
       <c r="F230" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="G230" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B231" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C231" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D231" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="E231" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F231" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="G231" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6103,22 +6238,22 @@
         <v>30</v>
       </c>
       <c r="B232" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C232" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="D232" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="E232" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F232" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G232" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6126,22 +6261,22 @@
         <v>30</v>
       </c>
       <c r="B233" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C233" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="D233" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="E233" t="s">
         <v>7</v>
       </c>
       <c r="F233" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G233" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6149,22 +6284,22 @@
         <v>30</v>
       </c>
       <c r="B234" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C234" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="D234" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="E234" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F234" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G234" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6172,22 +6307,22 @@
         <v>30</v>
       </c>
       <c r="B235" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C235" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D235" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="E235" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F235" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G235" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6195,22 +6330,22 @@
         <v>30</v>
       </c>
       <c r="B236" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C236" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="D236" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="E236" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="F236" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6218,22 +6353,22 @@
         <v>30</v>
       </c>
       <c r="B237" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C237" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="D237" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="E237" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F237" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="G237" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6241,22 +6376,22 @@
         <v>30</v>
       </c>
       <c r="B238" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C238" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="D238" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="E238" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="F238" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G238" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6264,68 +6399,68 @@
         <v>30</v>
       </c>
       <c r="B239" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C239" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="D239" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="E239" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F239" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G239" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B240" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C240" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D240" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E240" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F240" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="G240" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B241" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C241" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="D241" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="E241" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="F241" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6333,22 +6468,22 @@
         <v>31</v>
       </c>
       <c r="B242" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C242" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="D242" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="E242" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="G242" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6356,22 +6491,22 @@
         <v>31</v>
       </c>
       <c r="B243" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C243" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="D243" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="E243" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F243" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="G243" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6379,22 +6514,22 @@
         <v>31</v>
       </c>
       <c r="B244" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C244" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="D244" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="E244" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F244" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="G244" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6402,22 +6537,22 @@
         <v>31</v>
       </c>
       <c r="B245" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C245" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D245" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="E245" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F245" t="s">
         <v>8</v>
       </c>
       <c r="G245" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6425,22 +6560,22 @@
         <v>31</v>
       </c>
       <c r="B246" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C246" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="D246" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E246" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F246" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="G246" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6448,22 +6583,22 @@
         <v>31</v>
       </c>
       <c r="B247" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C247" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D247" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="E247" t="s">
         <v>7</v>
       </c>
       <c r="F247" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G247" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6471,22 +6606,22 @@
         <v>31</v>
       </c>
       <c r="B248" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C248" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="D248" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="E248" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F248" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G248" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6494,22 +6629,2115 @@
         <v>31</v>
       </c>
       <c r="B249" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C249" t="s">
+        <v>167</v>
+      </c>
+      <c r="D249" t="s">
+        <v>178</v>
+      </c>
+      <c r="E249" t="s">
+        <v>7</v>
+      </c>
+      <c r="F249" t="s">
+        <v>7</v>
+      </c>
+      <c r="G249" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>31</v>
+      </c>
+      <c r="B250" t="s">
+        <v>124</v>
+      </c>
+      <c r="C250" t="s">
+        <v>161</v>
+      </c>
+      <c r="D250" t="s">
+        <v>164</v>
+      </c>
+      <c r="E250" t="s">
+        <v>180</v>
+      </c>
+      <c r="F250" t="s">
+        <v>9</v>
+      </c>
+      <c r="G250" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>31</v>
+      </c>
+      <c r="B251" t="s">
+        <v>124</v>
+      </c>
+      <c r="C251" t="s">
+        <v>170</v>
+      </c>
+      <c r="D251" t="s">
+        <v>172</v>
+      </c>
+      <c r="E251" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" t="s">
+        <v>8</v>
+      </c>
+      <c r="G251" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>32</v>
+      </c>
+      <c r="B252" t="s">
         <v>125</v>
       </c>
-      <c r="D249" t="s">
+      <c r="C252" t="s">
+        <v>169</v>
+      </c>
+      <c r="D252" t="s">
+        <v>171</v>
+      </c>
+      <c r="E252" t="s">
+        <v>8</v>
+      </c>
+      <c r="F252" t="s">
+        <v>180</v>
+      </c>
+      <c r="G252" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>32</v>
+      </c>
+      <c r="B253" t="s">
+        <v>126</v>
+      </c>
+      <c r="C253" t="s">
+        <v>165</v>
+      </c>
+      <c r="D253" t="s">
+        <v>160</v>
+      </c>
+      <c r="E253" t="s">
+        <v>8</v>
+      </c>
+      <c r="F253" t="s">
+        <v>9</v>
+      </c>
+      <c r="G253" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>32</v>
+      </c>
+      <c r="B254" t="s">
+        <v>126</v>
+      </c>
+      <c r="C254" t="s">
+        <v>177</v>
+      </c>
+      <c r="D254" t="s">
+        <v>170</v>
+      </c>
+      <c r="E254" t="s">
+        <v>180</v>
+      </c>
+      <c r="F254" t="s">
+        <v>8</v>
+      </c>
+      <c r="G254" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>32</v>
+      </c>
+      <c r="B255" t="s">
+        <v>126</v>
+      </c>
+      <c r="C255" t="s">
+        <v>162</v>
+      </c>
+      <c r="D255" t="s">
+        <v>167</v>
+      </c>
+      <c r="E255" t="s">
+        <v>8</v>
+      </c>
+      <c r="F255" t="s">
+        <v>180</v>
+      </c>
+      <c r="G255" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" t="s">
+        <v>32</v>
+      </c>
+      <c r="B256" t="s">
         <v>127</v>
       </c>
-      <c r="E249" t="s">
+      <c r="C256" t="s">
+        <v>174</v>
+      </c>
+      <c r="D256" t="s">
+        <v>161</v>
+      </c>
+      <c r="E256" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" t="s">
+        <v>8</v>
+      </c>
+      <c r="G256" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>32</v>
+      </c>
+      <c r="B257" t="s">
+        <v>127</v>
+      </c>
+      <c r="C257" t="s">
+        <v>178</v>
+      </c>
+      <c r="D257" t="s">
+        <v>176</v>
+      </c>
+      <c r="E257" t="s">
+        <v>7</v>
+      </c>
+      <c r="F257" t="s">
+        <v>7</v>
+      </c>
+      <c r="G257" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" t="s">
+        <v>32</v>
+      </c>
+      <c r="B258" t="s">
+        <v>127</v>
+      </c>
+      <c r="C258" t="s">
+        <v>166</v>
+      </c>
+      <c r="D258" t="s">
+        <v>163</v>
+      </c>
+      <c r="E258" t="s">
+        <v>180</v>
+      </c>
+      <c r="F258" t="s">
         <v>10</v>
       </c>
-      <c r="F249" t="s">
-        <v>8</v>
-      </c>
-      <c r="G249" t="s">
+      <c r="G258" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>32</v>
+      </c>
+      <c r="B259" t="s">
+        <v>127</v>
+      </c>
+      <c r="C259" t="s">
+        <v>172</v>
+      </c>
+      <c r="D259" t="s">
+        <v>179</v>
+      </c>
+      <c r="E259" t="s">
+        <v>7</v>
+      </c>
+      <c r="F259" t="s">
+        <v>7</v>
+      </c>
+      <c r="G259" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" t="s">
+        <v>32</v>
+      </c>
+      <c r="B260" t="s">
+        <v>128</v>
+      </c>
+      <c r="C260" t="s">
+        <v>164</v>
+      </c>
+      <c r="D260" t="s">
+        <v>168</v>
+      </c>
+      <c r="E260" t="s">
+        <v>9</v>
+      </c>
+      <c r="F260" t="s">
+        <v>8</v>
+      </c>
+      <c r="G260" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>32</v>
+      </c>
+      <c r="B261" t="s">
+        <v>128</v>
+      </c>
+      <c r="C261" t="s">
+        <v>173</v>
+      </c>
+      <c r="D261" t="s">
+        <v>175</v>
+      </c>
+      <c r="E261" t="s">
+        <v>8</v>
+      </c>
+      <c r="F261" t="s">
+        <v>7</v>
+      </c>
+      <c r="G261" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>33</v>
+      </c>
+      <c r="B262" t="s">
+        <v>129</v>
+      </c>
+      <c r="C262" t="s">
+        <v>175</v>
+      </c>
+      <c r="D262" t="s">
+        <v>172</v>
+      </c>
+      <c r="E262" t="s">
+        <v>180</v>
+      </c>
+      <c r="F262" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" t="s">
+        <v>33</v>
+      </c>
+      <c r="B263" t="s">
+        <v>130</v>
+      </c>
+      <c r="C263" t="s">
+        <v>167</v>
+      </c>
+      <c r="D263" t="s">
+        <v>177</v>
+      </c>
+      <c r="E263" t="s">
+        <v>7</v>
+      </c>
+      <c r="F263" t="s">
+        <v>7</v>
+      </c>
+      <c r="G263" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>33</v>
+      </c>
+      <c r="B264" t="s">
+        <v>130</v>
+      </c>
+      <c r="C264" t="s">
+        <v>170</v>
+      </c>
+      <c r="D264" t="s">
+        <v>164</v>
+      </c>
+      <c r="E264" t="s">
+        <v>7</v>
+      </c>
+      <c r="F264" t="s">
+        <v>10</v>
+      </c>
+      <c r="G264" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>33</v>
+      </c>
+      <c r="B265" t="s">
+        <v>130</v>
+      </c>
+      <c r="C265" t="s">
+        <v>168</v>
+      </c>
+      <c r="D265" t="s">
+        <v>173</v>
+      </c>
+      <c r="E265" t="s">
+        <v>180</v>
+      </c>
+      <c r="F265" t="s">
+        <v>180</v>
+      </c>
+      <c r="G265" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>33</v>
+      </c>
+      <c r="B266" t="s">
+        <v>131</v>
+      </c>
+      <c r="C266" t="s">
+        <v>171</v>
+      </c>
+      <c r="D266" t="s">
+        <v>165</v>
+      </c>
+      <c r="E266" t="s">
+        <v>7</v>
+      </c>
+      <c r="F266" t="s">
+        <v>180</v>
+      </c>
+      <c r="G266" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>33</v>
+      </c>
+      <c r="B267" t="s">
+        <v>131</v>
+      </c>
+      <c r="C267" t="s">
+        <v>160</v>
+      </c>
+      <c r="D267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E267" t="s">
+        <v>180</v>
+      </c>
+      <c r="F267" t="s">
+        <v>7</v>
+      </c>
+      <c r="G267" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>33</v>
+      </c>
+      <c r="B268" t="s">
+        <v>131</v>
+      </c>
+      <c r="C268" t="s">
+        <v>161</v>
+      </c>
+      <c r="D268" t="s">
+        <v>166</v>
+      </c>
+      <c r="E268" t="s">
+        <v>7</v>
+      </c>
+      <c r="F268" t="s">
+        <v>7</v>
+      </c>
+      <c r="G268" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>33</v>
+      </c>
+      <c r="B269" t="s">
+        <v>131</v>
+      </c>
+      <c r="C269" t="s">
+        <v>179</v>
+      </c>
+      <c r="D269" t="s">
+        <v>169</v>
+      </c>
+      <c r="E269" t="s">
+        <v>7</v>
+      </c>
+      <c r="F269" t="s">
+        <v>8</v>
+      </c>
+      <c r="G269" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>33</v>
+      </c>
+      <c r="B270" t="s">
+        <v>131</v>
+      </c>
+      <c r="C270" t="s">
+        <v>176</v>
+      </c>
+      <c r="D270" t="s">
+        <v>174</v>
+      </c>
+      <c r="E270" t="s">
+        <v>8</v>
+      </c>
+      <c r="F270" t="s">
+        <v>7</v>
+      </c>
+      <c r="G270" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>33</v>
+      </c>
+      <c r="B271" t="s">
+        <v>132</v>
+      </c>
+      <c r="C271" t="s">
+        <v>163</v>
+      </c>
+      <c r="D271" t="s">
+        <v>162</v>
+      </c>
+      <c r="E271" t="s">
+        <v>8</v>
+      </c>
+      <c r="F271" t="s">
+        <v>7</v>
+      </c>
+      <c r="G271" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>34</v>
+      </c>
+      <c r="B272" t="s">
+        <v>133</v>
+      </c>
+      <c r="C272" t="s">
+        <v>176</v>
+      </c>
+      <c r="D272" t="s">
+        <v>168</v>
+      </c>
+      <c r="E272" t="s">
+        <v>7</v>
+      </c>
+      <c r="F272" t="s">
+        <v>7</v>
+      </c>
+      <c r="G272" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>34</v>
+      </c>
+      <c r="B273" t="s">
+        <v>134</v>
+      </c>
+      <c r="C273" t="s">
+        <v>178</v>
+      </c>
+      <c r="D273" t="s">
+        <v>177</v>
+      </c>
+      <c r="E273" t="s">
+        <v>10</v>
+      </c>
+      <c r="F273" t="s">
+        <v>8</v>
+      </c>
+      <c r="G273" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>34</v>
+      </c>
+      <c r="B274" t="s">
+        <v>134</v>
+      </c>
+      <c r="C274" t="s">
+        <v>165</v>
+      </c>
+      <c r="D274" t="s">
+        <v>161</v>
+      </c>
+      <c r="E274" t="s">
+        <v>7</v>
+      </c>
+      <c r="F274" t="s">
+        <v>180</v>
+      </c>
+      <c r="G274" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>34</v>
+      </c>
+      <c r="B275" t="s">
+        <v>134</v>
+      </c>
+      <c r="C275" t="s">
+        <v>169</v>
+      </c>
+      <c r="D275" t="s">
+        <v>163</v>
+      </c>
+      <c r="E275" t="s">
+        <v>180</v>
+      </c>
+      <c r="F275" t="s">
+        <v>7</v>
+      </c>
+      <c r="G275" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>34</v>
+      </c>
+      <c r="B276" t="s">
+        <v>134</v>
+      </c>
+      <c r="C276" t="s">
+        <v>162</v>
+      </c>
+      <c r="D276" t="s">
+        <v>170</v>
+      </c>
+      <c r="E276" t="s">
+        <v>8</v>
+      </c>
+      <c r="F276" t="s">
+        <v>9</v>
+      </c>
+      <c r="G276" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>34</v>
+      </c>
+      <c r="B277" t="s">
+        <v>135</v>
+      </c>
+      <c r="C277" t="s">
+        <v>166</v>
+      </c>
+      <c r="D277" t="s">
+        <v>171</v>
+      </c>
+      <c r="E277" t="s">
+        <v>180</v>
+      </c>
+      <c r="F277" t="s">
+        <v>7</v>
+      </c>
+      <c r="G277" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>34</v>
+      </c>
+      <c r="B278" t="s">
+        <v>135</v>
+      </c>
+      <c r="C278" t="s">
+        <v>172</v>
+      </c>
+      <c r="D278" t="s">
+        <v>160</v>
+      </c>
+      <c r="E278" t="s">
+        <v>7</v>
+      </c>
+      <c r="F278" t="s">
+        <v>180</v>
+      </c>
+      <c r="G278" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>34</v>
+      </c>
+      <c r="B279" t="s">
+        <v>135</v>
+      </c>
+      <c r="C279" t="s">
+        <v>174</v>
+      </c>
+      <c r="D279" t="s">
+        <v>179</v>
+      </c>
+      <c r="E279" t="s">
+        <v>8</v>
+      </c>
+      <c r="F279" t="s">
+        <v>8</v>
+      </c>
+      <c r="G279" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>34</v>
+      </c>
+      <c r="B280" t="s">
+        <v>135</v>
+      </c>
+      <c r="C280" t="s">
+        <v>173</v>
+      </c>
+      <c r="D280" t="s">
+        <v>164</v>
+      </c>
+      <c r="E280" t="s">
+        <v>8</v>
+      </c>
+      <c r="F280" t="s">
+        <v>8</v>
+      </c>
+      <c r="G280" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>34</v>
+      </c>
+      <c r="B281" t="s">
         <v>136</v>
+      </c>
+      <c r="C281" t="s">
+        <v>175</v>
+      </c>
+      <c r="D281" t="s">
+        <v>167</v>
+      </c>
+      <c r="E281" t="s">
+        <v>7</v>
+      </c>
+      <c r="F281" t="s">
+        <v>8</v>
+      </c>
+      <c r="G281" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>35</v>
+      </c>
+      <c r="B282" t="s">
+        <v>137</v>
+      </c>
+      <c r="C282" t="s">
+        <v>179</v>
+      </c>
+      <c r="D282" t="s">
+        <v>173</v>
+      </c>
+      <c r="E282" t="s">
+        <v>180</v>
+      </c>
+      <c r="F282" t="s">
+        <v>7</v>
+      </c>
+      <c r="G282" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>35</v>
+      </c>
+      <c r="B283" t="s">
+        <v>138</v>
+      </c>
+      <c r="C283" t="s">
+        <v>160</v>
+      </c>
+      <c r="D283" t="s">
+        <v>169</v>
+      </c>
+      <c r="E283" t="s">
+        <v>7</v>
+      </c>
+      <c r="F283" t="s">
+        <v>180</v>
+      </c>
+      <c r="G283" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>35</v>
+      </c>
+      <c r="B284" t="s">
+        <v>139</v>
+      </c>
+      <c r="C284" t="s">
+        <v>170</v>
+      </c>
+      <c r="D284" t="s">
+        <v>178</v>
+      </c>
+      <c r="E284" t="s">
+        <v>180</v>
+      </c>
+      <c r="F284" t="s">
+        <v>8</v>
+      </c>
+      <c r="G284" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>35</v>
+      </c>
+      <c r="B285" t="s">
+        <v>139</v>
+      </c>
+      <c r="C285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D285" t="s">
+        <v>168</v>
+      </c>
+      <c r="E285" t="s">
+        <v>180</v>
+      </c>
+      <c r="F285" t="s">
+        <v>7</v>
+      </c>
+      <c r="G285" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>35</v>
+      </c>
+      <c r="B286" t="s">
+        <v>139</v>
+      </c>
+      <c r="C286" t="s">
+        <v>177</v>
+      </c>
+      <c r="D286" t="s">
+        <v>166</v>
+      </c>
+      <c r="E286" t="s">
+        <v>8</v>
+      </c>
+      <c r="F286" t="s">
+        <v>9</v>
+      </c>
+      <c r="G286" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>35</v>
+      </c>
+      <c r="B287" t="s">
+        <v>139</v>
+      </c>
+      <c r="C287" t="s">
+        <v>161</v>
+      </c>
+      <c r="D287" t="s">
+        <v>175</v>
+      </c>
+      <c r="E287" t="s">
+        <v>180</v>
+      </c>
+      <c r="F287" t="s">
+        <v>180</v>
+      </c>
+      <c r="G287" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>35</v>
+      </c>
+      <c r="B288" t="s">
+        <v>140</v>
+      </c>
+      <c r="C288" t="s">
+        <v>174</v>
+      </c>
+      <c r="D288" t="s">
+        <v>162</v>
+      </c>
+      <c r="E288" t="s">
+        <v>7</v>
+      </c>
+      <c r="F288" t="s">
+        <v>9</v>
+      </c>
+      <c r="G288" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>35</v>
+      </c>
+      <c r="B289" t="s">
+        <v>140</v>
+      </c>
+      <c r="C289" t="s">
+        <v>171</v>
+      </c>
+      <c r="D289" t="s">
+        <v>172</v>
+      </c>
+      <c r="E289" t="s">
+        <v>7</v>
+      </c>
+      <c r="F289" t="s">
+        <v>180</v>
+      </c>
+      <c r="G289" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>35</v>
+      </c>
+      <c r="B290" t="s">
+        <v>140</v>
+      </c>
+      <c r="C290" t="s">
+        <v>164</v>
+      </c>
+      <c r="D290" t="s">
+        <v>165</v>
+      </c>
+      <c r="E290" t="s">
+        <v>7</v>
+      </c>
+      <c r="F290" t="s">
+        <v>7</v>
+      </c>
+      <c r="G290" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>36</v>
+      </c>
+      <c r="B291" t="s">
+        <v>141</v>
+      </c>
+      <c r="C291" t="s">
+        <v>176</v>
+      </c>
+      <c r="D291" t="s">
+        <v>179</v>
+      </c>
+      <c r="E291" t="s">
+        <v>180</v>
+      </c>
+      <c r="F291" t="s">
+        <v>9</v>
+      </c>
+      <c r="G291" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>36</v>
+      </c>
+      <c r="B292" t="s">
+        <v>141</v>
+      </c>
+      <c r="C292" t="s">
+        <v>162</v>
+      </c>
+      <c r="D292" t="s">
+        <v>161</v>
+      </c>
+      <c r="E292" t="s">
+        <v>7</v>
+      </c>
+      <c r="F292" t="s">
+        <v>7</v>
+      </c>
+      <c r="G292" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>36</v>
+      </c>
+      <c r="B293" t="s">
+        <v>141</v>
+      </c>
+      <c r="C293" t="s">
+        <v>168</v>
+      </c>
+      <c r="D293" t="s">
+        <v>170</v>
+      </c>
+      <c r="E293" t="s">
+        <v>7</v>
+      </c>
+      <c r="F293" t="s">
+        <v>180</v>
+      </c>
+      <c r="G293" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>36</v>
+      </c>
+      <c r="B294" t="s">
+        <v>141</v>
+      </c>
+      <c r="C294" t="s">
+        <v>175</v>
+      </c>
+      <c r="D294" t="s">
+        <v>174</v>
+      </c>
+      <c r="E294" t="s">
+        <v>7</v>
+      </c>
+      <c r="F294" t="s">
+        <v>180</v>
+      </c>
+      <c r="G294" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>36</v>
+      </c>
+      <c r="B295" t="s">
+        <v>141</v>
+      </c>
+      <c r="C295" t="s">
+        <v>173</v>
+      </c>
+      <c r="D295" t="s">
+        <v>172</v>
+      </c>
+      <c r="E295" t="s">
+        <v>7</v>
+      </c>
+      <c r="F295" t="s">
+        <v>8</v>
+      </c>
+      <c r="G295" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>36</v>
+      </c>
+      <c r="B296" t="s">
+        <v>142</v>
+      </c>
+      <c r="C296" t="s">
+        <v>169</v>
+      </c>
+      <c r="D296" t="s">
+        <v>177</v>
+      </c>
+      <c r="E296" t="s">
+        <v>9</v>
+      </c>
+      <c r="F296" t="s">
+        <v>180</v>
+      </c>
+      <c r="G296" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>36</v>
+      </c>
+      <c r="B297" t="s">
+        <v>142</v>
+      </c>
+      <c r="C297" t="s">
+        <v>178</v>
+      </c>
+      <c r="D297" t="s">
+        <v>171</v>
+      </c>
+      <c r="E297" t="s">
+        <v>7</v>
+      </c>
+      <c r="F297" t="s">
+        <v>7</v>
+      </c>
+      <c r="G297" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>36</v>
+      </c>
+      <c r="B298" t="s">
+        <v>142</v>
+      </c>
+      <c r="C298" t="s">
+        <v>165</v>
+      </c>
+      <c r="D298" t="s">
+        <v>167</v>
+      </c>
+      <c r="E298" t="s">
+        <v>7</v>
+      </c>
+      <c r="F298" t="s">
+        <v>7</v>
+      </c>
+      <c r="G298" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>36</v>
+      </c>
+      <c r="B299" t="s">
+        <v>142</v>
+      </c>
+      <c r="C299" t="s">
+        <v>166</v>
+      </c>
+      <c r="D299" t="s">
+        <v>164</v>
+      </c>
+      <c r="E299" t="s">
+        <v>180</v>
+      </c>
+      <c r="F299" t="s">
+        <v>180</v>
+      </c>
+      <c r="G299" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>36</v>
+      </c>
+      <c r="B300" t="s">
+        <v>142</v>
+      </c>
+      <c r="C300" t="s">
+        <v>163</v>
+      </c>
+      <c r="D300" t="s">
+        <v>160</v>
+      </c>
+      <c r="E300" t="s">
+        <v>8</v>
+      </c>
+      <c r="F300" t="s">
+        <v>180</v>
+      </c>
+      <c r="G300" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>37</v>
+      </c>
+      <c r="B301" t="s">
+        <v>143</v>
+      </c>
+      <c r="C301" t="s">
+        <v>177</v>
+      </c>
+      <c r="D301" t="s">
+        <v>165</v>
+      </c>
+      <c r="E301" t="s">
+        <v>8</v>
+      </c>
+      <c r="F301" t="s">
+        <v>8</v>
+      </c>
+      <c r="G301" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>37</v>
+      </c>
+      <c r="B302" t="s">
+        <v>144</v>
+      </c>
+      <c r="C302" t="s">
+        <v>172</v>
+      </c>
+      <c r="D302" t="s">
+        <v>166</v>
+      </c>
+      <c r="E302" t="s">
+        <v>9</v>
+      </c>
+      <c r="F302" t="s">
+        <v>180</v>
+      </c>
+      <c r="G302" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>37</v>
+      </c>
+      <c r="B303" t="s">
+        <v>144</v>
+      </c>
+      <c r="C303" t="s">
+        <v>164</v>
+      </c>
+      <c r="D303" t="s">
+        <v>175</v>
+      </c>
+      <c r="E303" t="s">
+        <v>7</v>
+      </c>
+      <c r="F303" t="s">
+        <v>180</v>
+      </c>
+      <c r="G303" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>37</v>
+      </c>
+      <c r="B304" t="s">
+        <v>144</v>
+      </c>
+      <c r="C304" t="s">
+        <v>160</v>
+      </c>
+      <c r="D304" t="s">
+        <v>168</v>
+      </c>
+      <c r="E304" t="s">
+        <v>9</v>
+      </c>
+      <c r="F304" t="s">
+        <v>8</v>
+      </c>
+      <c r="G304" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" t="s">
+        <v>37</v>
+      </c>
+      <c r="B305" t="s">
+        <v>145</v>
+      </c>
+      <c r="C305" t="s">
+        <v>161</v>
+      </c>
+      <c r="D305" t="s">
+        <v>169</v>
+      </c>
+      <c r="E305" t="s">
+        <v>180</v>
+      </c>
+      <c r="F305" t="s">
+        <v>180</v>
+      </c>
+      <c r="G305" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" t="s">
+        <v>37</v>
+      </c>
+      <c r="B306" t="s">
+        <v>145</v>
+      </c>
+      <c r="C306" t="s">
+        <v>170</v>
+      </c>
+      <c r="D306" t="s">
+        <v>176</v>
+      </c>
+      <c r="E306" t="s">
+        <v>8</v>
+      </c>
+      <c r="F306" t="s">
+        <v>10</v>
+      </c>
+      <c r="G306" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" t="s">
+        <v>37</v>
+      </c>
+      <c r="B307" t="s">
+        <v>145</v>
+      </c>
+      <c r="C307" t="s">
+        <v>178</v>
+      </c>
+      <c r="D307" t="s">
+        <v>179</v>
+      </c>
+      <c r="E307" t="s">
+        <v>8</v>
+      </c>
+      <c r="F307" t="s">
+        <v>7</v>
+      </c>
+      <c r="G307" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" t="s">
+        <v>37</v>
+      </c>
+      <c r="B308" t="s">
+        <v>145</v>
+      </c>
+      <c r="C308" t="s">
+        <v>171</v>
+      </c>
+      <c r="D308" t="s">
+        <v>162</v>
+      </c>
+      <c r="E308" t="s">
+        <v>7</v>
+      </c>
+      <c r="F308" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" t="s">
+        <v>37</v>
+      </c>
+      <c r="B309" t="s">
+        <v>145</v>
+      </c>
+      <c r="C309" t="s">
+        <v>174</v>
+      </c>
+      <c r="D309" t="s">
+        <v>173</v>
+      </c>
+      <c r="E309" t="s">
+        <v>7</v>
+      </c>
+      <c r="F309" t="s">
+        <v>180</v>
+      </c>
+      <c r="G309" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>37</v>
+      </c>
+      <c r="B310" t="s">
+        <v>146</v>
+      </c>
+      <c r="C310" t="s">
+        <v>167</v>
+      </c>
+      <c r="D310" t="s">
+        <v>163</v>
+      </c>
+      <c r="E310" t="s">
+        <v>7</v>
+      </c>
+      <c r="F310" t="s">
+        <v>8</v>
+      </c>
+      <c r="G310" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>38</v>
+      </c>
+      <c r="B311" t="s">
+        <v>147</v>
+      </c>
+      <c r="C311" t="s">
+        <v>175</v>
+      </c>
+      <c r="D311" t="s">
+        <v>177</v>
+      </c>
+      <c r="E311" t="s">
+        <v>10</v>
+      </c>
+      <c r="F311" t="s">
+        <v>7</v>
+      </c>
+      <c r="G311" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>38</v>
+      </c>
+      <c r="B312" t="s">
+        <v>148</v>
+      </c>
+      <c r="C312" t="s">
+        <v>166</v>
+      </c>
+      <c r="D312" t="s">
+        <v>160</v>
+      </c>
+      <c r="E312" t="s">
+        <v>7</v>
+      </c>
+      <c r="F312" t="s">
+        <v>180</v>
+      </c>
+      <c r="G312" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>38</v>
+      </c>
+      <c r="B313" t="s">
+        <v>148</v>
+      </c>
+      <c r="C313" t="s">
+        <v>168</v>
+      </c>
+      <c r="D313" t="s">
+        <v>174</v>
+      </c>
+      <c r="E313" t="s">
+        <v>180</v>
+      </c>
+      <c r="F313" t="s">
+        <v>180</v>
+      </c>
+      <c r="G313" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>38</v>
+      </c>
+      <c r="B314" t="s">
+        <v>148</v>
+      </c>
+      <c r="C314" t="s">
+        <v>169</v>
+      </c>
+      <c r="D314" t="s">
+        <v>170</v>
+      </c>
+      <c r="E314" t="s">
+        <v>180</v>
+      </c>
+      <c r="F314" t="s">
+        <v>180</v>
+      </c>
+      <c r="G314" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>38</v>
+      </c>
+      <c r="B315" t="s">
+        <v>149</v>
+      </c>
+      <c r="C315" t="s">
+        <v>176</v>
+      </c>
+      <c r="D315" t="s">
+        <v>161</v>
+      </c>
+      <c r="E315" t="s">
+        <v>8</v>
+      </c>
+      <c r="F315" t="s">
+        <v>8</v>
+      </c>
+      <c r="G315" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>38</v>
+      </c>
+      <c r="B316" t="s">
+        <v>149</v>
+      </c>
+      <c r="C316" t="s">
+        <v>165</v>
+      </c>
+      <c r="D316" t="s">
+        <v>172</v>
+      </c>
+      <c r="E316" t="s">
+        <v>9</v>
+      </c>
+      <c r="F316" t="s">
+        <v>9</v>
+      </c>
+      <c r="G316" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>38</v>
+      </c>
+      <c r="B317" t="s">
+        <v>149</v>
+      </c>
+      <c r="C317" t="s">
+        <v>163</v>
+      </c>
+      <c r="D317" t="s">
+        <v>178</v>
+      </c>
+      <c r="E317" t="s">
+        <v>8</v>
+      </c>
+      <c r="F317" t="s">
+        <v>8</v>
+      </c>
+      <c r="G317" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" t="s">
+        <v>38</v>
+      </c>
+      <c r="B318" t="s">
+        <v>150</v>
+      </c>
+      <c r="C318" t="s">
+        <v>173</v>
+      </c>
+      <c r="D318" t="s">
+        <v>162</v>
+      </c>
+      <c r="E318" t="s">
+        <v>7</v>
+      </c>
+      <c r="F318" t="s">
+        <v>7</v>
+      </c>
+      <c r="G318" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" t="s">
+        <v>38</v>
+      </c>
+      <c r="B319" t="s">
+        <v>150</v>
+      </c>
+      <c r="C319" t="s">
+        <v>179</v>
+      </c>
+      <c r="D319" t="s">
+        <v>171</v>
+      </c>
+      <c r="E319" t="s">
+        <v>8</v>
+      </c>
+      <c r="F319" t="s">
+        <v>8</v>
+      </c>
+      <c r="G319" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" t="s">
+        <v>38</v>
+      </c>
+      <c r="B320" t="s">
+        <v>151</v>
+      </c>
+      <c r="C320" t="s">
+        <v>167</v>
+      </c>
+      <c r="D320" t="s">
+        <v>164</v>
+      </c>
+      <c r="E320" t="s">
+        <v>7</v>
+      </c>
+      <c r="F320" t="s">
+        <v>8</v>
+      </c>
+      <c r="G320" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" t="s">
+        <v>39</v>
+      </c>
+      <c r="B321" t="s">
+        <v>152</v>
+      </c>
+      <c r="C321" t="s">
+        <v>162</v>
+      </c>
+      <c r="D321" t="s">
+        <v>175</v>
+      </c>
+      <c r="E321" t="s">
+        <v>180</v>
+      </c>
+      <c r="F321" t="s">
+        <v>7</v>
+      </c>
+      <c r="G321" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" t="s">
+        <v>39</v>
+      </c>
+      <c r="B322" t="s">
+        <v>152</v>
+      </c>
+      <c r="C322" t="s">
+        <v>178</v>
+      </c>
+      <c r="D322" t="s">
+        <v>174</v>
+      </c>
+      <c r="E322" t="s">
+        <v>8</v>
+      </c>
+      <c r="F322" t="s">
+        <v>8</v>
+      </c>
+      <c r="G322" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" t="s">
+        <v>39</v>
+      </c>
+      <c r="B323" t="s">
+        <v>153</v>
+      </c>
+      <c r="C323" t="s">
+        <v>160</v>
+      </c>
+      <c r="D323" t="s">
+        <v>176</v>
+      </c>
+      <c r="E323" t="s">
+        <v>7</v>
+      </c>
+      <c r="F323" t="s">
+        <v>180</v>
+      </c>
+      <c r="G323" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" t="s">
+        <v>39</v>
+      </c>
+      <c r="B324" t="s">
+        <v>153</v>
+      </c>
+      <c r="C324" t="s">
+        <v>171</v>
+      </c>
+      <c r="D324" t="s">
+        <v>167</v>
+      </c>
+      <c r="E324" t="s">
+        <v>7</v>
+      </c>
+      <c r="F324" t="s">
+        <v>180</v>
+      </c>
+      <c r="G324" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" t="s">
+        <v>39</v>
+      </c>
+      <c r="B325" t="s">
+        <v>154</v>
+      </c>
+      <c r="C325" t="s">
+        <v>165</v>
+      </c>
+      <c r="D325" t="s">
+        <v>166</v>
+      </c>
+      <c r="E325" t="s">
+        <v>180</v>
+      </c>
+      <c r="F325" t="s">
+        <v>9</v>
+      </c>
+      <c r="G325" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" t="s">
+        <v>39</v>
+      </c>
+      <c r="B326" t="s">
+        <v>154</v>
+      </c>
+      <c r="C326" t="s">
+        <v>168</v>
+      </c>
+      <c r="D326" t="s">
+        <v>161</v>
+      </c>
+      <c r="E326" t="s">
+        <v>180</v>
+      </c>
+      <c r="F326" t="s">
+        <v>180</v>
+      </c>
+      <c r="G326" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" t="s">
+        <v>39</v>
+      </c>
+      <c r="B327" t="s">
+        <v>154</v>
+      </c>
+      <c r="C327" t="s">
+        <v>177</v>
+      </c>
+      <c r="D327" t="s">
+        <v>173</v>
+      </c>
+      <c r="E327" t="s">
+        <v>180</v>
+      </c>
+      <c r="F327" t="s">
+        <v>8</v>
+      </c>
+      <c r="G327" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" t="s">
+        <v>39</v>
+      </c>
+      <c r="B328" t="s">
+        <v>154</v>
+      </c>
+      <c r="C328" t="s">
+        <v>170</v>
+      </c>
+      <c r="D328" t="s">
+        <v>179</v>
+      </c>
+      <c r="E328" t="s">
+        <v>7</v>
+      </c>
+      <c r="F328" t="s">
+        <v>8</v>
+      </c>
+      <c r="G328" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" t="s">
+        <v>39</v>
+      </c>
+      <c r="B329" t="s">
+        <v>155</v>
+      </c>
+      <c r="C329" t="s">
+        <v>164</v>
+      </c>
+      <c r="D329" t="s">
+        <v>169</v>
+      </c>
+      <c r="E329" t="s">
+        <v>7</v>
+      </c>
+      <c r="F329" t="s">
+        <v>9</v>
+      </c>
+      <c r="G329" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" t="s">
+        <v>39</v>
+      </c>
+      <c r="B330" t="s">
+        <v>155</v>
+      </c>
+      <c r="C330" t="s">
+        <v>172</v>
+      </c>
+      <c r="D330" t="s">
+        <v>163</v>
+      </c>
+      <c r="E330" t="s">
+        <v>7</v>
+      </c>
+      <c r="F330" t="s">
+        <v>8</v>
+      </c>
+      <c r="G330" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" t="s">
+        <v>40</v>
+      </c>
+      <c r="B331" t="s">
+        <v>156</v>
+      </c>
+      <c r="C331" t="s">
+        <v>161</v>
+      </c>
+      <c r="D331" t="s">
+        <v>177</v>
+      </c>
+      <c r="E331" t="s">
+        <v>9</v>
+      </c>
+      <c r="F331" t="s">
+        <v>180</v>
+      </c>
+      <c r="G331" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" t="s">
+        <v>40</v>
+      </c>
+      <c r="B332" t="s">
+        <v>157</v>
+      </c>
+      <c r="C332" t="s">
+        <v>166</v>
+      </c>
+      <c r="D332" t="s">
+        <v>170</v>
+      </c>
+      <c r="E332" t="s">
+        <v>7</v>
+      </c>
+      <c r="F332" t="s">
+        <v>7</v>
+      </c>
+      <c r="G332" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" t="s">
+        <v>40</v>
+      </c>
+      <c r="B333" t="s">
+        <v>157</v>
+      </c>
+      <c r="C333" t="s">
+        <v>174</v>
+      </c>
+      <c r="D333" t="s">
+        <v>172</v>
+      </c>
+      <c r="E333" t="s">
+        <v>180</v>
+      </c>
+      <c r="F333" t="s">
+        <v>180</v>
+      </c>
+      <c r="G333" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" t="s">
+        <v>40</v>
+      </c>
+      <c r="B334" t="s">
+        <v>157</v>
+      </c>
+      <c r="C334" t="s">
+        <v>175</v>
+      </c>
+      <c r="D334" t="s">
+        <v>171</v>
+      </c>
+      <c r="E334" t="s">
+        <v>7</v>
+      </c>
+      <c r="F334" t="s">
+        <v>180</v>
+      </c>
+      <c r="G334" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" t="s">
+        <v>40</v>
+      </c>
+      <c r="B335" t="s">
+        <v>158</v>
+      </c>
+      <c r="C335" t="s">
+        <v>163</v>
+      </c>
+      <c r="D335" t="s">
+        <v>168</v>
+      </c>
+      <c r="E335" t="s">
+        <v>8</v>
+      </c>
+      <c r="F335" t="s">
+        <v>180</v>
+      </c>
+      <c r="G335" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" t="s">
+        <v>40</v>
+      </c>
+      <c r="B336" t="s">
+        <v>158</v>
+      </c>
+      <c r="C336" t="s">
+        <v>169</v>
+      </c>
+      <c r="D336" t="s">
+        <v>167</v>
+      </c>
+      <c r="E336" t="s">
+        <v>7</v>
+      </c>
+      <c r="F336" t="s">
+        <v>7</v>
+      </c>
+      <c r="G336" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" t="s">
+        <v>40</v>
+      </c>
+      <c r="B337" t="s">
+        <v>158</v>
+      </c>
+      <c r="C337" t="s">
+        <v>179</v>
+      </c>
+      <c r="D337" t="s">
+        <v>160</v>
+      </c>
+      <c r="E337" t="s">
+        <v>8</v>
+      </c>
+      <c r="F337" t="s">
+        <v>180</v>
+      </c>
+      <c r="G337" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" t="s">
+        <v>40</v>
+      </c>
+      <c r="B338" t="s">
+        <v>158</v>
+      </c>
+      <c r="C338" t="s">
+        <v>176</v>
+      </c>
+      <c r="D338" t="s">
+        <v>164</v>
+      </c>
+      <c r="E338" t="s">
+        <v>8</v>
+      </c>
+      <c r="F338" t="s">
+        <v>8</v>
+      </c>
+      <c r="G338" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" t="s">
+        <v>40</v>
+      </c>
+      <c r="B339" t="s">
+        <v>158</v>
+      </c>
+      <c r="C339" t="s">
+        <v>173</v>
+      </c>
+      <c r="D339" t="s">
+        <v>165</v>
+      </c>
+      <c r="E339" t="s">
+        <v>11</v>
+      </c>
+      <c r="F339" t="s">
+        <v>7</v>
+      </c>
+      <c r="G339" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" t="s">
+        <v>40</v>
+      </c>
+      <c r="B340" t="s">
+        <v>159</v>
+      </c>
+      <c r="C340" t="s">
+        <v>162</v>
+      </c>
+      <c r="D340" t="s">
+        <v>178</v>
+      </c>
+      <c r="E340" t="s">
+        <v>9</v>
+      </c>
+      <c r="F340" t="s">
+        <v>180</v>
+      </c>
+      <c r="G340" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/season/season-2324_csv.xlsx
+++ b/season/season-2324_csv.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="196">
   <si>
     <t>Giornata</t>
   </si>
@@ -139,6 +139,15 @@
     <t>34</t>
   </si>
   <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>2023-08-19</t>
   </si>
   <si>
@@ -427,9 +436,6 @@
     <t>2024-03-11</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>2024-03-15</t>
   </si>
   <si>
@@ -494,6 +500,42 @@
   </si>
   <si>
     <t>2024-04-29</t>
+  </si>
+  <si>
+    <t>2024-05-03</t>
+  </si>
+  <si>
+    <t>2024-05-04</t>
+  </si>
+  <si>
+    <t>2024-05-05</t>
+  </si>
+  <si>
+    <t>2024-05-06</t>
+  </si>
+  <si>
+    <t>2024-05-10</t>
+  </si>
+  <si>
+    <t>2024-05-11</t>
+  </si>
+  <si>
+    <t>2024-05-12</t>
+  </si>
+  <si>
+    <t>2024-05-13</t>
+  </si>
+  <si>
+    <t>2024-05-17</t>
+  </si>
+  <si>
+    <t>2024-05-18</t>
+  </si>
+  <si>
+    <t>2024-05-19</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
   </si>
   <si>
     <t>Empoli</t>
@@ -917,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G340"/>
+  <dimension ref="A1:G370"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -948,22 +990,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -971,13 +1013,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -986,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -994,13 +1036,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1009,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1017,22 +1059,22 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G5" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1040,13 +1082,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1055,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1063,22 +1105,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1086,13 +1128,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1101,7 +1143,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1109,22 +1151,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1132,22 +1174,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1155,22 +1197,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F11" t="s">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1178,13 +1220,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1193,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1201,22 +1243,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G13" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1224,13 +1266,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1239,7 +1281,7 @@
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1247,13 +1289,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -1262,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1270,13 +1312,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1285,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1293,13 +1335,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -1308,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1316,22 +1358,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
       </c>
       <c r="G18" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1339,22 +1381,22 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G19" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1362,13 +1404,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -1377,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1385,22 +1427,22 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1408,13 +1450,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1423,7 +1465,7 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1431,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -1446,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1454,13 +1496,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1469,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="G24" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1477,22 +1519,22 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F25" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G25" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1500,22 +1542,22 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G26" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1523,13 +1565,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -1538,7 +1580,7 @@
         <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1546,22 +1588,22 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G28" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1569,22 +1611,22 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G29" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1592,22 +1634,22 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1615,22 +1657,22 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D31" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1638,13 +1680,13 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -1653,7 +1695,7 @@
         <v>7</v>
       </c>
       <c r="G32" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1661,13 +1703,13 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
@@ -1676,7 +1718,7 @@
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1684,13 +1726,13 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -1699,7 +1741,7 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1707,22 +1749,22 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G35" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1730,13 +1772,13 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -1745,7 +1787,7 @@
         <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1753,13 +1795,13 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -1768,7 +1810,7 @@
         <v>7</v>
       </c>
       <c r="G37" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1776,13 +1818,13 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -1791,7 +1833,7 @@
         <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1799,22 +1841,22 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
         <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G39" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1822,22 +1864,22 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s">
         <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1845,22 +1887,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G41" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1868,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -1883,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1891,22 +1933,22 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G43" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1914,22 +1956,22 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G44" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1937,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D45" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -1952,7 +1994,7 @@
         <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1960,13 +2002,13 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -1975,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="G46" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1983,22 +2025,22 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
       </c>
       <c r="G47" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2006,22 +2048,22 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G48" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2029,22 +2071,22 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F49" t="s">
         <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2052,22 +2094,22 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E50" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F50" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G50" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2075,13 +2117,13 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D51" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -2090,7 +2132,7 @@
         <v>7</v>
       </c>
       <c r="G51" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2098,22 +2140,22 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2121,13 +2163,13 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -2136,7 +2178,7 @@
         <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2144,22 +2186,22 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D54" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2167,22 +2209,22 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D55" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2190,13 +2232,13 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -2205,7 +2247,7 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2213,22 +2255,22 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G57" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2236,13 +2278,13 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -2251,7 +2293,7 @@
         <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2259,13 +2301,13 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D59" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -2274,7 +2316,7 @@
         <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2282,22 +2324,22 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D60" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E60" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G60" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2305,13 +2347,13 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -2320,7 +2362,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2328,22 +2370,22 @@
         <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D62" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E62" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F62" t="s">
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2351,22 +2393,22 @@
         <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D63" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G63" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2374,22 +2416,22 @@
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
         <v>177</v>
       </c>
-      <c r="D64" t="s">
-        <v>163</v>
-      </c>
       <c r="E64" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
       </c>
       <c r="G64" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2397,22 +2439,22 @@
         <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G65" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2420,13 +2462,13 @@
         <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -2435,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="G66" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2443,22 +2485,22 @@
         <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C67" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D67" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F67" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G67" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2466,22 +2508,22 @@
         <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G68" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2489,22 +2531,22 @@
         <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E69" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
       </c>
       <c r="G69" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2512,22 +2554,22 @@
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F70" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G70" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2535,22 +2577,22 @@
         <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C71" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G71" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2558,22 +2600,22 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C72" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E72" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F72" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G72" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2581,13 +2623,13 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D73" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -2596,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="G73" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2604,13 +2646,13 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -2619,7 +2661,7 @@
         <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2627,22 +2669,22 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D75" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G75" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2650,22 +2692,22 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E76" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2673,22 +2715,22 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C77" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D77" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G77" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2696,13 +2738,13 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C78" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -2711,7 +2753,7 @@
         <v>7</v>
       </c>
       <c r="G78" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2719,13 +2761,13 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -2734,7 +2776,7 @@
         <v>8</v>
       </c>
       <c r="G79" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2742,13 +2784,13 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C80" t="s">
+        <v>192</v>
+      </c>
+      <c r="D80" t="s">
         <v>178</v>
-      </c>
-      <c r="D80" t="s">
-        <v>164</v>
       </c>
       <c r="E80" t="s">
         <v>7</v>
@@ -2757,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="G80" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2765,13 +2807,13 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D81" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E81" t="s">
         <v>7</v>
@@ -2780,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2788,13 +2830,13 @@
         <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D82" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E82" t="s">
         <v>7</v>
@@ -2803,7 +2845,7 @@
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2811,22 +2853,22 @@
         <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D83" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E83" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2834,22 +2876,22 @@
         <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E84" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F84" t="s">
         <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2857,22 +2899,22 @@
         <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C85" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E85" t="s">
         <v>7</v>
       </c>
       <c r="F85" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G85" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2880,13 +2922,13 @@
         <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -2895,7 +2937,7 @@
         <v>7</v>
       </c>
       <c r="G86" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2903,13 +2945,13 @@
         <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D87" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -2918,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="G87" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2926,22 +2968,22 @@
         <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C88" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D88" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G88" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2949,22 +2991,22 @@
         <v>15</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C89" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E89" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F89" t="s">
         <v>7</v>
       </c>
       <c r="G89" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2972,13 +3014,13 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C90" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D90" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E90" t="s">
         <v>7</v>
@@ -2987,7 +3029,7 @@
         <v>7</v>
       </c>
       <c r="G90" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2995,22 +3037,22 @@
         <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C91" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D91" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E91" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3018,22 +3060,22 @@
         <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
       </c>
       <c r="F92" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G92" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3041,13 +3083,13 @@
         <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D93" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -3056,7 +3098,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3064,22 +3106,22 @@
         <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C94" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D94" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E94" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F94" t="s">
         <v>7</v>
       </c>
       <c r="G94" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3087,22 +3129,22 @@
         <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C95" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D95" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
       </c>
       <c r="F95" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G95" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3110,13 +3152,13 @@
         <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C96" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D96" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -3125,7 +3167,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3133,13 +3175,13 @@
         <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C97" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D97" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -3148,7 +3190,7 @@
         <v>7</v>
       </c>
       <c r="G97" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3156,22 +3198,22 @@
         <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C98" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D98" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
       </c>
       <c r="F98" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G98" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3179,13 +3221,13 @@
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C99" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D99" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -3194,7 +3236,7 @@
         <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3202,22 +3244,22 @@
         <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C100" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D100" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E100" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F100" t="s">
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3225,22 +3267,22 @@
         <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D101" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E101" t="s">
         <v>7</v>
       </c>
       <c r="F101" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G101" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3248,22 +3290,22 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C102" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E102" t="s">
         <v>7</v>
       </c>
       <c r="F102" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G102" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3271,22 +3313,22 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C103" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D103" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E103" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
       </c>
       <c r="G103" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3294,13 +3336,13 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C104" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D104" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E104" t="s">
         <v>7</v>
@@ -3309,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3317,22 +3359,22 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C105" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E105" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F105" t="s">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3340,13 +3382,13 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D106" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E106" t="s">
         <v>7</v>
@@ -3355,7 +3397,7 @@
         <v>9</v>
       </c>
       <c r="G106" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3363,13 +3405,13 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C107" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -3378,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="G107" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3386,13 +3428,13 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D108" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -3401,7 +3443,7 @@
         <v>7</v>
       </c>
       <c r="G108" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3409,22 +3451,22 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C109" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D109" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E109" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F109" t="s">
         <v>7</v>
       </c>
       <c r="G109" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3432,13 +3474,13 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D110" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -3447,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="G110" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3455,13 +3497,13 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D111" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -3470,7 +3512,7 @@
         <v>7</v>
       </c>
       <c r="G111" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3478,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B112" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C112" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D112" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -3493,7 +3535,7 @@
         <v>8</v>
       </c>
       <c r="G112" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3501,22 +3543,22 @@
         <v>18</v>
       </c>
       <c r="B113" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C113" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D113" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E113" t="s">
         <v>7</v>
       </c>
       <c r="F113" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G113" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3524,13 +3566,13 @@
         <v>18</v>
       </c>
       <c r="B114" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C114" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D114" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -3539,7 +3581,7 @@
         <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3547,13 +3589,13 @@
         <v>18</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C115" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D115" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -3562,7 +3604,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3570,13 +3612,13 @@
         <v>18</v>
       </c>
       <c r="B116" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C116" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D116" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E116" t="s">
         <v>7</v>
@@ -3585,7 +3627,7 @@
         <v>7</v>
       </c>
       <c r="G116" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3593,22 +3635,22 @@
         <v>18</v>
       </c>
       <c r="B117" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C117" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D117" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E117" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F117" t="s">
         <v>7</v>
       </c>
       <c r="G117" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3616,13 +3658,13 @@
         <v>18</v>
       </c>
       <c r="B118" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C118" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D118" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -3631,7 +3673,7 @@
         <v>7</v>
       </c>
       <c r="G118" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3639,13 +3681,13 @@
         <v>18</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C119" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D119" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E119" t="s">
         <v>7</v>
@@ -3654,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="G119" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3662,22 +3704,22 @@
         <v>18</v>
       </c>
       <c r="B120" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C120" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D120" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E120" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F120" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G120" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3685,22 +3727,22 @@
         <v>18</v>
       </c>
       <c r="B121" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D121" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
       </c>
       <c r="F121" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G121" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3708,13 +3750,13 @@
         <v>19</v>
       </c>
       <c r="B122" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C122" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -3723,7 +3765,7 @@
         <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3731,13 +3773,13 @@
         <v>19</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C123" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D123" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E123" t="s">
         <v>7</v>
@@ -3746,7 +3788,7 @@
         <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3754,22 +3796,22 @@
         <v>19</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C124" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D124" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E124" t="s">
         <v>7</v>
       </c>
       <c r="F124" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G124" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3777,13 +3819,13 @@
         <v>19</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C125" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D125" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E125" t="s">
         <v>7</v>
@@ -3792,7 +3834,7 @@
         <v>7</v>
       </c>
       <c r="G125" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3800,13 +3842,13 @@
         <v>19</v>
       </c>
       <c r="B126" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D126" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -3815,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="G126" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3823,13 +3865,13 @@
         <v>19</v>
       </c>
       <c r="B127" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D127" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -3838,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="G127" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3846,13 +3888,13 @@
         <v>19</v>
       </c>
       <c r="B128" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D128" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -3861,7 +3903,7 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3869,13 +3911,13 @@
         <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C129" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D129" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E129" t="s">
         <v>7</v>
@@ -3884,7 +3926,7 @@
         <v>7</v>
       </c>
       <c r="G129" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3892,13 +3934,13 @@
         <v>19</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C130" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D130" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -3907,7 +3949,7 @@
         <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3915,22 +3957,22 @@
         <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C131" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D131" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
       </c>
       <c r="F131" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G131" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3938,13 +3980,13 @@
         <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D132" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E132" t="s">
         <v>7</v>
@@ -3953,7 +3995,7 @@
         <v>8</v>
       </c>
       <c r="G132" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3961,13 +4003,13 @@
         <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C133" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D133" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E133" t="s">
         <v>7</v>
@@ -3976,7 +4018,7 @@
         <v>7</v>
       </c>
       <c r="G133" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3984,22 +4026,22 @@
         <v>20</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C134" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D134" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E134" t="s">
         <v>7</v>
       </c>
       <c r="F134" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G134" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4007,13 +4049,13 @@
         <v>20</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C135" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D135" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -4022,7 +4064,7 @@
         <v>7</v>
       </c>
       <c r="G135" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4030,13 +4072,13 @@
         <v>20</v>
       </c>
       <c r="B136" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D136" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E136" t="s">
         <v>7</v>
@@ -4045,7 +4087,7 @@
         <v>7</v>
       </c>
       <c r="G136" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4053,22 +4095,22 @@
         <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D137" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
       </c>
       <c r="F137" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G137" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4076,13 +4118,13 @@
         <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D138" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -4091,7 +4133,7 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4099,13 +4141,13 @@
         <v>20</v>
       </c>
       <c r="B139" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D139" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E139" t="s">
         <v>7</v>
@@ -4114,7 +4156,7 @@
         <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4122,22 +4164,22 @@
         <v>20</v>
       </c>
       <c r="B140" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D140" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E140" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F140" t="s">
         <v>9</v>
       </c>
       <c r="G140" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4145,22 +4187,22 @@
         <v>20</v>
       </c>
       <c r="B141" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C141" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D141" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G141" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4168,22 +4210,22 @@
         <v>21</v>
       </c>
       <c r="B142" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D142" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E142" t="s">
         <v>7</v>
       </c>
       <c r="F142" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G142" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4191,13 +4233,13 @@
         <v>21</v>
       </c>
       <c r="B143" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C143" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D143" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E143" t="s">
         <v>7</v>
@@ -4206,7 +4248,7 @@
         <v>7</v>
       </c>
       <c r="G143" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4214,13 +4256,13 @@
         <v>21</v>
       </c>
       <c r="B144" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C144" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D144" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -4229,7 +4271,7 @@
         <v>8</v>
       </c>
       <c r="G144" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4237,22 +4279,22 @@
         <v>21</v>
       </c>
       <c r="B145" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D145" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G145" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4260,22 +4302,22 @@
         <v>21</v>
       </c>
       <c r="B146" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C146" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D146" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E146" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F146" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G146" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4283,22 +4325,22 @@
         <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C147" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D147" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E147" t="s">
         <v>7</v>
       </c>
       <c r="F147" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G147" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4306,13 +4348,13 @@
         <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C148" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D148" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E148" t="s">
         <v>7</v>
@@ -4321,7 +4363,7 @@
         <v>8</v>
       </c>
       <c r="G148" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4329,13 +4371,13 @@
         <v>21</v>
       </c>
       <c r="B149" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C149" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D149" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E149" t="s">
         <v>7</v>
@@ -4344,7 +4386,7 @@
         <v>7</v>
       </c>
       <c r="G149" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4352,13 +4394,13 @@
         <v>21</v>
       </c>
       <c r="B150" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C150" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D150" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E150" t="s">
         <v>7</v>
@@ -4367,7 +4409,7 @@
         <v>7</v>
       </c>
       <c r="G150" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4375,13 +4417,13 @@
         <v>21</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C151" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D151" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -4390,7 +4432,7 @@
         <v>7</v>
       </c>
       <c r="G151" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4398,13 +4440,13 @@
         <v>22</v>
       </c>
       <c r="B152" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D152" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E152" t="s">
         <v>7</v>
@@ -4413,7 +4455,7 @@
         <v>7</v>
       </c>
       <c r="G152" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4421,13 +4463,13 @@
         <v>22</v>
       </c>
       <c r="B153" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C153" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D153" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -4436,7 +4478,7 @@
         <v>7</v>
       </c>
       <c r="G153" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4444,13 +4486,13 @@
         <v>22</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C154" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D154" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -4459,7 +4501,7 @@
         <v>7</v>
       </c>
       <c r="G154" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4467,22 +4509,22 @@
         <v>22</v>
       </c>
       <c r="B155" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C155" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D155" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E155" t="s">
         <v>7</v>
       </c>
       <c r="F155" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G155" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4490,22 +4532,22 @@
         <v>22</v>
       </c>
       <c r="B156" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D156" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G156" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4513,22 +4555,22 @@
         <v>22</v>
       </c>
       <c r="B157" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C157" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D157" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E157" t="s">
         <v>7</v>
       </c>
       <c r="F157" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G157" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4536,13 +4578,13 @@
         <v>22</v>
       </c>
       <c r="B158" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D158" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -4551,7 +4593,7 @@
         <v>8</v>
       </c>
       <c r="G158" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4559,22 +4601,22 @@
         <v>22</v>
       </c>
       <c r="B159" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D159" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
       </c>
       <c r="F159" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G159" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4582,22 +4624,22 @@
         <v>22</v>
       </c>
       <c r="B160" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D160" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E160" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F160" t="s">
         <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4605,13 +4647,13 @@
         <v>22</v>
       </c>
       <c r="B161" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C161" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D161" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -4620,7 +4662,7 @@
         <v>7</v>
       </c>
       <c r="G161" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4628,22 +4670,22 @@
         <v>23</v>
       </c>
       <c r="B162" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C162" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D162" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E162" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F162" t="s">
         <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4651,13 +4693,13 @@
         <v>23</v>
       </c>
       <c r="B163" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C163" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D163" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E163" t="s">
         <v>7</v>
@@ -4666,7 +4708,7 @@
         <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4674,22 +4716,22 @@
         <v>23</v>
       </c>
       <c r="B164" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D164" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E164" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F164" t="s">
         <v>7</v>
       </c>
       <c r="G164" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4697,13 +4739,13 @@
         <v>23</v>
       </c>
       <c r="B165" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C165" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D165" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -4712,7 +4754,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4720,13 +4762,13 @@
         <v>23</v>
       </c>
       <c r="B166" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C166" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D166" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E166" t="s">
         <v>7</v>
@@ -4735,7 +4777,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4743,22 +4785,22 @@
         <v>23</v>
       </c>
       <c r="B167" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D167" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E167" t="s">
         <v>7</v>
       </c>
       <c r="F167" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G167" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4766,13 +4808,13 @@
         <v>23</v>
       </c>
       <c r="B168" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C168" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D168" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E168" t="s">
         <v>7</v>
@@ -4781,7 +4823,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4789,22 +4831,22 @@
         <v>23</v>
       </c>
       <c r="B169" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C169" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D169" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
       </c>
       <c r="F169" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G169" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4812,22 +4854,22 @@
         <v>23</v>
       </c>
       <c r="B170" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D170" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
       </c>
       <c r="F170" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G170" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4835,22 +4877,22 @@
         <v>23</v>
       </c>
       <c r="B171" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C171" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D171" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
       </c>
       <c r="F171" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G171" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4858,22 +4900,22 @@
         <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C172" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D172" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E172" t="s">
         <v>7</v>
       </c>
       <c r="F172" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G172" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4881,22 +4923,22 @@
         <v>24</v>
       </c>
       <c r="B173" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C173" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D173" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E173" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F173" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G173" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4904,13 +4946,13 @@
         <v>24</v>
       </c>
       <c r="B174" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C174" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D174" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E174" t="s">
         <v>7</v>
@@ -4919,7 +4961,7 @@
         <v>7</v>
       </c>
       <c r="G174" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4927,13 +4969,13 @@
         <v>24</v>
       </c>
       <c r="B175" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C175" t="s">
+        <v>189</v>
+      </c>
+      <c r="D175" t="s">
         <v>175</v>
-      </c>
-      <c r="D175" t="s">
-        <v>161</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
@@ -4942,7 +4984,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4950,22 +4992,22 @@
         <v>24</v>
       </c>
       <c r="B176" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C176" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D176" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E176" t="s">
         <v>7</v>
       </c>
       <c r="F176" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G176" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4973,22 +5015,22 @@
         <v>24</v>
       </c>
       <c r="B177" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C177" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D177" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E177" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F177" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G177" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4996,22 +5038,22 @@
         <v>24</v>
       </c>
       <c r="B178" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C178" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D178" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
       </c>
       <c r="F178" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G178" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5019,22 +5061,22 @@
         <v>24</v>
       </c>
       <c r="B179" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C179" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D179" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E179" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F179" t="s">
         <v>7</v>
       </c>
       <c r="G179" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5042,22 +5084,22 @@
         <v>24</v>
       </c>
       <c r="B180" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C180" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D180" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E180" t="s">
         <v>7</v>
       </c>
       <c r="F180" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G180" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5065,22 +5107,22 @@
         <v>24</v>
       </c>
       <c r="B181" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C181" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D181" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E181" t="s">
         <v>7</v>
       </c>
       <c r="F181" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G181" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5088,13 +5130,13 @@
         <v>25</v>
       </c>
       <c r="B182" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C182" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D182" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E182" t="s">
         <v>7</v>
@@ -5103,7 +5145,7 @@
         <v>7</v>
       </c>
       <c r="G182" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5111,13 +5153,13 @@
         <v>25</v>
       </c>
       <c r="B183" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D183" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -5126,7 +5168,7 @@
         <v>7</v>
       </c>
       <c r="G183" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5134,13 +5176,13 @@
         <v>25</v>
       </c>
       <c r="B184" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C184" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D184" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -5149,7 +5191,7 @@
         <v>9</v>
       </c>
       <c r="G184" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5157,13 +5199,13 @@
         <v>25</v>
       </c>
       <c r="B185" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C185" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D185" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E185" t="s">
         <v>7</v>
@@ -5172,7 +5214,7 @@
         <v>7</v>
       </c>
       <c r="G185" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5180,22 +5222,22 @@
         <v>25</v>
       </c>
       <c r="B186" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C186" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D186" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E186" t="s">
         <v>7</v>
       </c>
       <c r="F186" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G186" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5203,22 +5245,22 @@
         <v>25</v>
       </c>
       <c r="B187" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C187" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D187" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E187" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F187" t="s">
         <v>9</v>
       </c>
       <c r="G187" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5226,22 +5268,22 @@
         <v>25</v>
       </c>
       <c r="B188" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C188" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D188" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
       </c>
       <c r="F188" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G188" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5249,13 +5291,13 @@
         <v>25</v>
       </c>
       <c r="B189" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C189" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D189" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E189" t="s">
         <v>7</v>
@@ -5264,7 +5306,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5272,13 +5314,13 @@
         <v>25</v>
       </c>
       <c r="B190" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C190" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D190" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E190" t="s">
         <v>7</v>
@@ -5287,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="G190" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5295,13 +5337,13 @@
         <v>25</v>
       </c>
       <c r="B191" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C191" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D191" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E191" t="s">
         <v>7</v>
@@ -5310,7 +5352,7 @@
         <v>7</v>
       </c>
       <c r="G191" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5318,22 +5360,22 @@
         <v>26</v>
       </c>
       <c r="B192" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C192" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D192" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E192" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F192" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G192" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5341,13 +5383,13 @@
         <v>26</v>
       </c>
       <c r="B193" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C193" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D193" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -5356,7 +5398,7 @@
         <v>7</v>
       </c>
       <c r="G193" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5364,13 +5406,13 @@
         <v>26</v>
       </c>
       <c r="B194" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C194" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D194" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -5379,7 +5421,7 @@
         <v>7</v>
       </c>
       <c r="G194" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5387,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="B195" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C195" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D195" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E195" t="s">
         <v>7</v>
@@ -5402,7 +5444,7 @@
         <v>11</v>
       </c>
       <c r="G195" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5410,22 +5452,22 @@
         <v>26</v>
       </c>
       <c r="B196" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C196" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D196" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E196" t="s">
         <v>7</v>
       </c>
       <c r="F196" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G196" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5433,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="B197" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C197" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D197" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -5448,7 +5490,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5456,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="B198" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C198" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D198" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -5471,7 +5513,7 @@
         <v>8</v>
       </c>
       <c r="G198" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5479,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="B199" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C199" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D199" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
@@ -5494,7 +5536,7 @@
         <v>7</v>
       </c>
       <c r="G199" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5502,22 +5544,22 @@
         <v>26</v>
       </c>
       <c r="B200" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C200" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D200" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E200" t="s">
         <v>11</v>
       </c>
       <c r="F200" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G200" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5525,22 +5567,22 @@
         <v>26</v>
       </c>
       <c r="B201" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C201" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D201" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
       </c>
       <c r="F201" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G201" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5548,13 +5590,13 @@
         <v>27</v>
       </c>
       <c r="B202" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C202" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D202" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -5563,7 +5605,7 @@
         <v>7</v>
       </c>
       <c r="G202" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5571,13 +5613,13 @@
         <v>27</v>
       </c>
       <c r="B203" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C203" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D203" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -5586,7 +5628,7 @@
         <v>9</v>
       </c>
       <c r="G203" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5594,13 +5636,13 @@
         <v>27</v>
       </c>
       <c r="B204" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C204" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -5609,7 +5651,7 @@
         <v>7</v>
       </c>
       <c r="G204" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5617,22 +5659,22 @@
         <v>27</v>
       </c>
       <c r="B205" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C205" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D205" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
       </c>
       <c r="F205" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G205" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5640,13 +5682,13 @@
         <v>27</v>
       </c>
       <c r="B206" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C206" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D206" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E206" t="s">
         <v>7</v>
@@ -5655,7 +5697,7 @@
         <v>8</v>
       </c>
       <c r="G206" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5663,22 +5705,22 @@
         <v>27</v>
       </c>
       <c r="B207" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C207" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D207" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E207" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F207" t="s">
         <v>9</v>
       </c>
       <c r="G207" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5686,22 +5728,22 @@
         <v>27</v>
       </c>
       <c r="B208" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C208" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
       </c>
       <c r="F208" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G208" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5709,22 +5751,22 @@
         <v>27</v>
       </c>
       <c r="B209" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C209" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D209" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E209" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F209" t="s">
         <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5732,13 +5774,13 @@
         <v>27</v>
       </c>
       <c r="B210" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C210" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D210" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E210" t="s">
         <v>7</v>
@@ -5747,7 +5789,7 @@
         <v>12</v>
       </c>
       <c r="G210" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5755,22 +5797,22 @@
         <v>27</v>
       </c>
       <c r="B211" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D211" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
       </c>
       <c r="F211" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5778,13 +5820,13 @@
         <v>28</v>
       </c>
       <c r="B212" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D212" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E212" t="s">
         <v>7</v>
@@ -5793,7 +5835,7 @@
         <v>8</v>
       </c>
       <c r="G212" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5801,22 +5843,22 @@
         <v>28</v>
       </c>
       <c r="B213" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C213" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D213" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
       </c>
       <c r="F213" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G213" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5824,14 +5866,14 @@
         <v>28</v>
       </c>
       <c r="B214" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C214" t="s">
+        <v>188</v>
+      </c>
+      <c r="D214" t="s">
         <v>174</v>
       </c>
-      <c r="D214" t="s">
-        <v>160</v>
-      </c>
       <c r="E214" t="s">
         <v>7</v>
       </c>
@@ -5839,7 +5881,7 @@
         <v>7</v>
       </c>
       <c r="G214" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5847,13 +5889,13 @@
         <v>28</v>
       </c>
       <c r="B215" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C215" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D215" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -5862,7 +5904,7 @@
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5870,13 +5912,13 @@
         <v>28</v>
       </c>
       <c r="B216" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C216" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D216" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -5885,7 +5927,7 @@
         <v>7</v>
       </c>
       <c r="G216" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5893,13 +5935,13 @@
         <v>28</v>
       </c>
       <c r="B217" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C217" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D217" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E217" t="s">
         <v>7</v>
@@ -5908,7 +5950,7 @@
         <v>7</v>
       </c>
       <c r="G217" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5916,22 +5958,22 @@
         <v>28</v>
       </c>
       <c r="B218" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D218" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E218" t="s">
         <v>7</v>
       </c>
       <c r="F218" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G218" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5939,22 +5981,22 @@
         <v>28</v>
       </c>
       <c r="B219" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C219" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D219" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E219" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F219" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G219" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5962,22 +6004,22 @@
         <v>28</v>
       </c>
       <c r="B220" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D220" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E220" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
       </c>
       <c r="G220" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5985,13 +6027,13 @@
         <v>28</v>
       </c>
       <c r="B221" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C221" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D221" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E221" t="s">
         <v>7</v>
@@ -6000,7 +6042,7 @@
         <v>8</v>
       </c>
       <c r="G221" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6008,13 +6050,13 @@
         <v>29</v>
       </c>
       <c r="B222" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C222" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E222" t="s">
         <v>9</v>
@@ -6023,7 +6065,7 @@
         <v>8</v>
       </c>
       <c r="G222" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6031,22 +6073,22 @@
         <v>29</v>
       </c>
       <c r="B223" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C223" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D223" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E223" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F223" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G223" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6054,22 +6096,22 @@
         <v>29</v>
       </c>
       <c r="B224" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C224" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D224" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E224" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F224" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G224" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6077,13 +6119,13 @@
         <v>29</v>
       </c>
       <c r="B225" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C225" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D225" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -6092,7 +6134,7 @@
         <v>9</v>
       </c>
       <c r="G225" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6100,13 +6142,13 @@
         <v>29</v>
       </c>
       <c r="B226" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C226" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D226" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E226" t="s">
         <v>10</v>
@@ -6115,7 +6157,7 @@
         <v>8</v>
       </c>
       <c r="G226" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6123,22 +6165,22 @@
         <v>29</v>
       </c>
       <c r="B227" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C227" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D227" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E227" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F227" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G227" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6146,13 +6188,13 @@
         <v>29</v>
       </c>
       <c r="B228" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C228" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D228" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -6161,7 +6203,7 @@
         <v>7</v>
       </c>
       <c r="G228" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6169,13 +6211,13 @@
         <v>29</v>
       </c>
       <c r="B229" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D229" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E229" t="s">
         <v>9</v>
@@ -6184,7 +6226,7 @@
         <v>7</v>
       </c>
       <c r="G229" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6192,22 +6234,22 @@
         <v>29</v>
       </c>
       <c r="B230" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E230" t="s">
         <v>7</v>
       </c>
       <c r="F230" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G230" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6215,22 +6257,22 @@
         <v>29</v>
       </c>
       <c r="B231" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C231" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D231" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E231" t="s">
         <v>10</v>
       </c>
       <c r="F231" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G231" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6238,13 +6280,13 @@
         <v>30</v>
       </c>
       <c r="B232" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C232" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D232" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E232" t="s">
         <v>7</v>
@@ -6253,7 +6295,7 @@
         <v>9</v>
       </c>
       <c r="G232" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6261,13 +6303,13 @@
         <v>30</v>
       </c>
       <c r="B233" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C233" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D233" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E233" t="s">
         <v>7</v>
@@ -6276,7 +6318,7 @@
         <v>9</v>
       </c>
       <c r="G233" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6284,13 +6326,13 @@
         <v>30</v>
       </c>
       <c r="B234" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C234" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D234" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -6299,7 +6341,7 @@
         <v>10</v>
       </c>
       <c r="G234" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6307,13 +6349,13 @@
         <v>30</v>
       </c>
       <c r="B235" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C235" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D235" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E235" t="s">
         <v>7</v>
@@ -6322,7 +6364,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6330,13 +6372,13 @@
         <v>30</v>
       </c>
       <c r="B236" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C236" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D236" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E236" t="s">
         <v>11</v>
@@ -6345,7 +6387,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6353,22 +6395,22 @@
         <v>30</v>
       </c>
       <c r="B237" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C237" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D237" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E237" t="s">
         <v>10</v>
       </c>
       <c r="F237" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G237" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6376,22 +6418,22 @@
         <v>30</v>
       </c>
       <c r="B238" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C238" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D238" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E238" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F238" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G238" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6399,13 +6441,13 @@
         <v>30</v>
       </c>
       <c r="B239" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C239" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D239" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E239" t="s">
         <v>7</v>
@@ -6414,7 +6456,7 @@
         <v>10</v>
       </c>
       <c r="G239" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6422,22 +6464,22 @@
         <v>30</v>
       </c>
       <c r="B240" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C240" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D240" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E240" t="s">
         <v>7</v>
       </c>
       <c r="F240" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G240" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6445,22 +6487,22 @@
         <v>30</v>
       </c>
       <c r="B241" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C241" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D241" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E241" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F241" t="s">
         <v>7</v>
       </c>
       <c r="G241" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6468,22 +6510,22 @@
         <v>31</v>
       </c>
       <c r="B242" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C242" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D242" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
       </c>
       <c r="F242" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G242" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6491,22 +6533,22 @@
         <v>31</v>
       </c>
       <c r="B243" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C243" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D243" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E243" t="s">
         <v>10</v>
       </c>
       <c r="F243" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6514,14 +6556,14 @@
         <v>31</v>
       </c>
       <c r="B244" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C244" t="s">
+        <v>190</v>
+      </c>
+      <c r="D244" t="s">
         <v>176</v>
       </c>
-      <c r="D244" t="s">
-        <v>162</v>
-      </c>
       <c r="E244" t="s">
         <v>7</v>
       </c>
@@ -6529,7 +6571,7 @@
         <v>7</v>
       </c>
       <c r="G244" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6537,13 +6579,13 @@
         <v>31</v>
       </c>
       <c r="B245" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C245" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D245" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -6552,7 +6594,7 @@
         <v>8</v>
       </c>
       <c r="G245" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6560,22 +6602,22 @@
         <v>31</v>
       </c>
       <c r="B246" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C246" t="s">
+        <v>193</v>
+      </c>
+      <c r="D246" t="s">
         <v>179</v>
-      </c>
-      <c r="D246" t="s">
-        <v>165</v>
       </c>
       <c r="E246" t="s">
         <v>9</v>
       </c>
       <c r="F246" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G246" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6583,13 +6625,13 @@
         <v>31</v>
       </c>
       <c r="B247" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C247" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D247" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E247" t="s">
         <v>7</v>
@@ -6598,7 +6640,7 @@
         <v>8</v>
       </c>
       <c r="G247" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6606,13 +6648,13 @@
         <v>31</v>
       </c>
       <c r="B248" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C248" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D248" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E248" t="s">
         <v>7</v>
@@ -6621,7 +6663,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6629,13 +6671,13 @@
         <v>31</v>
       </c>
       <c r="B249" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C249" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D249" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E249" t="s">
         <v>7</v>
@@ -6644,7 +6686,7 @@
         <v>7</v>
       </c>
       <c r="G249" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6652,22 +6694,22 @@
         <v>31</v>
       </c>
       <c r="B250" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C250" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D250" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E250" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F250" t="s">
         <v>9</v>
       </c>
       <c r="G250" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6675,13 +6717,13 @@
         <v>31</v>
       </c>
       <c r="B251" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C251" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D251" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
@@ -6690,7 +6732,7 @@
         <v>8</v>
       </c>
       <c r="G251" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6698,22 +6740,22 @@
         <v>32</v>
       </c>
       <c r="B252" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C252" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
       </c>
       <c r="F252" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G252" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6721,13 +6763,13 @@
         <v>32</v>
       </c>
       <c r="B253" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C253" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D253" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -6736,7 +6778,7 @@
         <v>9</v>
       </c>
       <c r="G253" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6744,22 +6786,22 @@
         <v>32</v>
       </c>
       <c r="B254" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C254" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D254" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E254" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F254" t="s">
         <v>8</v>
       </c>
       <c r="G254" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6767,22 +6809,22 @@
         <v>32</v>
       </c>
       <c r="B255" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C255" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D255" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
       </c>
       <c r="F255" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G255" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6790,13 +6832,13 @@
         <v>32</v>
       </c>
       <c r="B256" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C256" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D256" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E256" t="s">
         <v>9</v>
@@ -6805,7 +6847,7 @@
         <v>8</v>
       </c>
       <c r="G256" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6813,13 +6855,13 @@
         <v>32</v>
       </c>
       <c r="B257" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C257" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D257" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E257" t="s">
         <v>7</v>
@@ -6828,7 +6870,7 @@
         <v>7</v>
       </c>
       <c r="G257" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -6836,22 +6878,22 @@
         <v>32</v>
       </c>
       <c r="B258" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C258" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D258" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E258" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F258" t="s">
         <v>10</v>
       </c>
       <c r="G258" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -6859,13 +6901,13 @@
         <v>32</v>
       </c>
       <c r="B259" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C259" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E259" t="s">
         <v>7</v>
@@ -6874,7 +6916,7 @@
         <v>7</v>
       </c>
       <c r="G259" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -6882,13 +6924,13 @@
         <v>32</v>
       </c>
       <c r="B260" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C260" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D260" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E260" t="s">
         <v>9</v>
@@ -6897,7 +6939,7 @@
         <v>8</v>
       </c>
       <c r="G260" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -6905,13 +6947,13 @@
         <v>32</v>
       </c>
       <c r="B261" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C261" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D261" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -6920,7 +6962,7 @@
         <v>7</v>
       </c>
       <c r="G261" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -6928,22 +6970,22 @@
         <v>33</v>
       </c>
       <c r="B262" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C262" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D262" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E262" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F262" t="s">
         <v>7</v>
       </c>
       <c r="G262" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -6951,13 +6993,13 @@
         <v>33</v>
       </c>
       <c r="B263" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C263" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D263" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E263" t="s">
         <v>7</v>
@@ -6966,7 +7008,7 @@
         <v>7</v>
       </c>
       <c r="G263" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -6974,13 +7016,13 @@
         <v>33</v>
       </c>
       <c r="B264" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C264" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D264" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E264" t="s">
         <v>7</v>
@@ -6989,7 +7031,7 @@
         <v>10</v>
       </c>
       <c r="G264" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -6997,22 +7039,22 @@
         <v>33</v>
       </c>
       <c r="B265" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C265" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D265" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E265" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F265" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G265" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7020,22 +7062,22 @@
         <v>33</v>
       </c>
       <c r="B266" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C266" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D266" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E266" t="s">
         <v>7</v>
       </c>
       <c r="F266" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G266" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7043,22 +7085,22 @@
         <v>33</v>
       </c>
       <c r="B267" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C267" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D267" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E267" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F267" t="s">
         <v>7</v>
       </c>
       <c r="G267" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7066,13 +7108,13 @@
         <v>33</v>
       </c>
       <c r="B268" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C268" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D268" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E268" t="s">
         <v>7</v>
@@ -7081,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="G268" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7089,13 +7131,13 @@
         <v>33</v>
       </c>
       <c r="B269" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C269" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D269" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E269" t="s">
         <v>7</v>
@@ -7104,7 +7146,7 @@
         <v>8</v>
       </c>
       <c r="G269" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7112,13 +7154,13 @@
         <v>33</v>
       </c>
       <c r="B270" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C270" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D270" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -7127,7 +7169,7 @@
         <v>7</v>
       </c>
       <c r="G270" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7135,13 +7177,13 @@
         <v>33</v>
       </c>
       <c r="B271" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C271" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D271" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -7150,7 +7192,7 @@
         <v>7</v>
       </c>
       <c r="G271" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7158,13 +7200,13 @@
         <v>34</v>
       </c>
       <c r="B272" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C272" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D272" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E272" t="s">
         <v>7</v>
@@ -7173,7 +7215,7 @@
         <v>7</v>
       </c>
       <c r="G272" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7181,13 +7223,13 @@
         <v>34</v>
       </c>
       <c r="B273" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C273" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D273" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
@@ -7196,7 +7238,7 @@
         <v>8</v>
       </c>
       <c r="G273" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7204,22 +7246,22 @@
         <v>34</v>
       </c>
       <c r="B274" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C274" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D274" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E274" t="s">
         <v>7</v>
       </c>
       <c r="F274" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G274" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7227,22 +7269,22 @@
         <v>34</v>
       </c>
       <c r="B275" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C275" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D275" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E275" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F275" t="s">
         <v>7</v>
       </c>
       <c r="G275" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7250,13 +7292,13 @@
         <v>34</v>
       </c>
       <c r="B276" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C276" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D276" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -7265,7 +7307,7 @@
         <v>9</v>
       </c>
       <c r="G276" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7273,22 +7315,22 @@
         <v>34</v>
       </c>
       <c r="B277" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C277" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D277" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E277" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F277" t="s">
         <v>7</v>
       </c>
       <c r="G277" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7296,22 +7338,22 @@
         <v>34</v>
       </c>
       <c r="B278" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C278" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D278" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E278" t="s">
         <v>7</v>
       </c>
       <c r="F278" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G278" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7319,13 +7361,13 @@
         <v>34</v>
       </c>
       <c r="B279" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C279" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D279" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -7334,7 +7376,7 @@
         <v>8</v>
       </c>
       <c r="G279" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7342,13 +7384,13 @@
         <v>34</v>
       </c>
       <c r="B280" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C280" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D280" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -7357,7 +7399,7 @@
         <v>8</v>
       </c>
       <c r="G280" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7365,13 +7407,13 @@
         <v>34</v>
       </c>
       <c r="B281" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C281" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D281" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E281" t="s">
         <v>7</v>
@@ -7380,7 +7422,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7388,22 +7430,22 @@
         <v>35</v>
       </c>
       <c r="B282" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C282" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D282" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E282" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F282" t="s">
         <v>7</v>
       </c>
       <c r="G282" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7411,22 +7453,22 @@
         <v>35</v>
       </c>
       <c r="B283" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C283" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D283" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E283" t="s">
         <v>7</v>
       </c>
       <c r="F283" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G283" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7434,22 +7476,22 @@
         <v>35</v>
       </c>
       <c r="B284" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C284" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D284" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E284" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F284" t="s">
         <v>8</v>
       </c>
       <c r="G284" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7457,22 +7499,22 @@
         <v>35</v>
       </c>
       <c r="B285" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C285" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="D285" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E285" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F285" t="s">
         <v>7</v>
       </c>
       <c r="G285" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7480,13 +7522,13 @@
         <v>35</v>
       </c>
       <c r="B286" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C286" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D286" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -7495,7 +7537,7 @@
         <v>9</v>
       </c>
       <c r="G286" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7503,22 +7545,22 @@
         <v>35</v>
       </c>
       <c r="B287" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C287" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="D287" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E287" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F287" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G287" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7526,13 +7568,13 @@
         <v>35</v>
       </c>
       <c r="B288" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C288" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D288" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="E288" t="s">
         <v>7</v>
@@ -7541,7 +7583,7 @@
         <v>9</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7549,22 +7591,22 @@
         <v>35</v>
       </c>
       <c r="B289" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C289" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D289" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E289" t="s">
         <v>7</v>
       </c>
       <c r="F289" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G289" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7572,13 +7614,13 @@
         <v>35</v>
       </c>
       <c r="B290" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C290" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D290" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E290" t="s">
         <v>7</v>
@@ -7587,7 +7629,7 @@
         <v>7</v>
       </c>
       <c r="G290" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7595,22 +7637,22 @@
         <v>36</v>
       </c>
       <c r="B291" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C291" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D291" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E291" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F291" t="s">
         <v>9</v>
       </c>
       <c r="G291" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7618,13 +7660,13 @@
         <v>36</v>
       </c>
       <c r="B292" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C292" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D292" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E292" t="s">
         <v>7</v>
@@ -7633,7 +7675,7 @@
         <v>7</v>
       </c>
       <c r="G292" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7641,22 +7683,22 @@
         <v>36</v>
       </c>
       <c r="B293" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C293" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D293" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E293" t="s">
         <v>7</v>
       </c>
       <c r="F293" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G293" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7664,22 +7706,22 @@
         <v>36</v>
       </c>
       <c r="B294" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C294" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D294" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E294" t="s">
         <v>7</v>
       </c>
       <c r="F294" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G294" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7687,13 +7729,13 @@
         <v>36</v>
       </c>
       <c r="B295" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C295" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D295" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E295" t="s">
         <v>7</v>
@@ -7702,7 +7744,7 @@
         <v>8</v>
       </c>
       <c r="G295" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7710,22 +7752,22 @@
         <v>36</v>
       </c>
       <c r="B296" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C296" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D296" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E296" t="s">
         <v>9</v>
       </c>
       <c r="F296" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G296" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7733,13 +7775,13 @@
         <v>36</v>
       </c>
       <c r="B297" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C297" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D297" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E297" t="s">
         <v>7</v>
@@ -7748,7 +7790,7 @@
         <v>7</v>
       </c>
       <c r="G297" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7756,13 +7798,13 @@
         <v>36</v>
       </c>
       <c r="B298" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C298" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D298" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E298" t="s">
         <v>7</v>
@@ -7771,7 +7813,7 @@
         <v>7</v>
       </c>
       <c r="G298" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7779,22 +7821,22 @@
         <v>36</v>
       </c>
       <c r="B299" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C299" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D299" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E299" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F299" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G299" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7802,22 +7844,22 @@
         <v>36</v>
       </c>
       <c r="B300" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C300" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D300" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
       </c>
       <c r="F300" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G300" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7825,13 +7867,13 @@
         <v>37</v>
       </c>
       <c r="B301" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C301" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D301" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -7840,7 +7882,7 @@
         <v>8</v>
       </c>
       <c r="G301" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7848,22 +7890,22 @@
         <v>37</v>
       </c>
       <c r="B302" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C302" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D302" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E302" t="s">
         <v>9</v>
       </c>
       <c r="F302" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G302" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7871,22 +7913,22 @@
         <v>37</v>
       </c>
       <c r="B303" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C303" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D303" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E303" t="s">
         <v>7</v>
       </c>
       <c r="F303" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7894,13 +7936,13 @@
         <v>37</v>
       </c>
       <c r="B304" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C304" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D304" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E304" t="s">
         <v>9</v>
@@ -7909,7 +7951,7 @@
         <v>8</v>
       </c>
       <c r="G304" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7917,22 +7959,22 @@
         <v>37</v>
       </c>
       <c r="B305" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C305" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D305" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E305" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F305" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G305" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7940,13 +7982,13 @@
         <v>37</v>
       </c>
       <c r="B306" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C306" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D306" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -7955,7 +7997,7 @@
         <v>10</v>
       </c>
       <c r="G306" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7963,13 +8005,13 @@
         <v>37</v>
       </c>
       <c r="B307" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C307" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D307" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -7978,7 +8020,7 @@
         <v>7</v>
       </c>
       <c r="G307" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7986,13 +8028,13 @@
         <v>37</v>
       </c>
       <c r="B308" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C308" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D308" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E308" t="s">
         <v>7</v>
@@ -8001,7 +8043,7 @@
         <v>8</v>
       </c>
       <c r="G308" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -8009,22 +8051,22 @@
         <v>37</v>
       </c>
       <c r="B309" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C309" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D309" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E309" t="s">
         <v>7</v>
       </c>
       <c r="F309" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G309" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -8032,13 +8074,13 @@
         <v>37</v>
       </c>
       <c r="B310" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C310" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D310" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E310" t="s">
         <v>7</v>
@@ -8047,7 +8089,7 @@
         <v>8</v>
       </c>
       <c r="G310" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -8055,13 +8097,13 @@
         <v>38</v>
       </c>
       <c r="B311" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C311" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D311" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E311" t="s">
         <v>10</v>
@@ -8070,7 +8112,7 @@
         <v>7</v>
       </c>
       <c r="G311" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -8078,22 +8120,22 @@
         <v>38</v>
       </c>
       <c r="B312" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C312" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D312" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E312" t="s">
         <v>7</v>
       </c>
       <c r="F312" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G312" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -8101,22 +8143,22 @@
         <v>38</v>
       </c>
       <c r="B313" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C313" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D313" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E313" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F313" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G313" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8124,22 +8166,22 @@
         <v>38</v>
       </c>
       <c r="B314" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C314" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D314" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E314" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F314" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G314" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -8147,13 +8189,13 @@
         <v>38</v>
       </c>
       <c r="B315" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C315" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D315" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -8162,7 +8204,7 @@
         <v>8</v>
       </c>
       <c r="G315" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8170,13 +8212,13 @@
         <v>38</v>
       </c>
       <c r="B316" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C316" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D316" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E316" t="s">
         <v>9</v>
@@ -8185,7 +8227,7 @@
         <v>9</v>
       </c>
       <c r="G316" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -8193,13 +8235,13 @@
         <v>38</v>
       </c>
       <c r="B317" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C317" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D317" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E317" t="s">
         <v>8</v>
@@ -8208,7 +8250,7 @@
         <v>8</v>
       </c>
       <c r="G317" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8216,13 +8258,13 @@
         <v>38</v>
       </c>
       <c r="B318" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C318" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D318" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E318" t="s">
         <v>7</v>
@@ -8231,7 +8273,7 @@
         <v>7</v>
       </c>
       <c r="G318" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8239,13 +8281,13 @@
         <v>38</v>
       </c>
       <c r="B319" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C319" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D319" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -8254,7 +8296,7 @@
         <v>8</v>
       </c>
       <c r="G319" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8262,13 +8304,13 @@
         <v>38</v>
       </c>
       <c r="B320" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C320" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D320" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E320" t="s">
         <v>7</v>
@@ -8277,7 +8319,7 @@
         <v>8</v>
       </c>
       <c r="G320" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -8285,22 +8327,22 @@
         <v>39</v>
       </c>
       <c r="B321" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C321" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D321" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E321" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F321" t="s">
         <v>7</v>
       </c>
       <c r="G321" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -8308,13 +8350,13 @@
         <v>39</v>
       </c>
       <c r="B322" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C322" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D322" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -8323,7 +8365,7 @@
         <v>8</v>
       </c>
       <c r="G322" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -8331,22 +8373,22 @@
         <v>39</v>
       </c>
       <c r="B323" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C323" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D323" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E323" t="s">
         <v>7</v>
       </c>
       <c r="F323" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G323" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -8354,22 +8396,22 @@
         <v>39</v>
       </c>
       <c r="B324" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C324" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="D324" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E324" t="s">
         <v>7</v>
       </c>
       <c r="F324" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G324" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -8377,22 +8419,22 @@
         <v>39</v>
       </c>
       <c r="B325" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C325" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D325" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E325" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F325" t="s">
         <v>9</v>
       </c>
       <c r="G325" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -8400,22 +8442,22 @@
         <v>39</v>
       </c>
       <c r="B326" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C326" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D326" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E326" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F326" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G326" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -8423,22 +8465,22 @@
         <v>39</v>
       </c>
       <c r="B327" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C327" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D327" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E327" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F327" t="s">
         <v>8</v>
       </c>
       <c r="G327" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -8446,13 +8488,13 @@
         <v>39</v>
       </c>
       <c r="B328" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C328" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D328" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E328" t="s">
         <v>7</v>
@@ -8461,7 +8503,7 @@
         <v>8</v>
       </c>
       <c r="G328" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -8469,13 +8511,13 @@
         <v>39</v>
       </c>
       <c r="B329" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C329" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D329" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E329" t="s">
         <v>7</v>
@@ -8484,7 +8526,7 @@
         <v>9</v>
       </c>
       <c r="G329" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -8492,13 +8534,13 @@
         <v>39</v>
       </c>
       <c r="B330" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C330" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D330" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E330" t="s">
         <v>7</v>
@@ -8507,7 +8549,7 @@
         <v>8</v>
       </c>
       <c r="G330" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -8515,22 +8557,22 @@
         <v>40</v>
       </c>
       <c r="B331" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C331" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D331" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E331" t="s">
         <v>9</v>
       </c>
       <c r="F331" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G331" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -8538,13 +8580,13 @@
         <v>40</v>
       </c>
       <c r="B332" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C332" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D332" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E332" t="s">
         <v>7</v>
@@ -8553,7 +8595,7 @@
         <v>7</v>
       </c>
       <c r="G332" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -8561,22 +8603,22 @@
         <v>40</v>
       </c>
       <c r="B333" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C333" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D333" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="E333" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F333" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G333" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -8584,22 +8626,22 @@
         <v>40</v>
       </c>
       <c r="B334" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C334" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D334" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E334" t="s">
         <v>7</v>
       </c>
       <c r="F334" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G334" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -8607,22 +8649,22 @@
         <v>40</v>
       </c>
       <c r="B335" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C335" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D335" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
       </c>
       <c r="F335" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G335" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -8630,13 +8672,13 @@
         <v>40</v>
       </c>
       <c r="B336" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C336" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D336" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E336" t="s">
         <v>7</v>
@@ -8645,7 +8687,7 @@
         <v>7</v>
       </c>
       <c r="G336" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -8653,22 +8695,22 @@
         <v>40</v>
       </c>
       <c r="B337" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C337" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D337" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
       </c>
       <c r="F337" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G337" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -8676,13 +8718,13 @@
         <v>40</v>
       </c>
       <c r="B338" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C338" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D338" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -8691,7 +8733,7 @@
         <v>8</v>
       </c>
       <c r="G338" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="339" spans="1:7">
@@ -8699,13 +8741,13 @@
         <v>40</v>
       </c>
       <c r="B339" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C339" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D339" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E339" t="s">
         <v>11</v>
@@ -8714,7 +8756,7 @@
         <v>7</v>
       </c>
       <c r="G339" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -8722,22 +8764,712 @@
         <v>40</v>
       </c>
       <c r="B340" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C340" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D340" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E340" t="s">
         <v>9</v>
       </c>
       <c r="F340" t="s">
+        <v>194</v>
+      </c>
+      <c r="G340" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" t="s">
+        <v>41</v>
+      </c>
+      <c r="B341" t="s">
+        <v>162</v>
+      </c>
+      <c r="C341" t="s">
+        <v>182</v>
+      </c>
+      <c r="D341" t="s">
+        <v>183</v>
+      </c>
+      <c r="E341" t="s">
+        <v>194</v>
+      </c>
+      <c r="F341" t="s">
+        <v>194</v>
+      </c>
+      <c r="G341" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" t="s">
+        <v>41</v>
+      </c>
+      <c r="B342" t="s">
+        <v>163</v>
+      </c>
+      <c r="C342" t="s">
+        <v>184</v>
+      </c>
+      <c r="D342" t="s">
+        <v>189</v>
+      </c>
+      <c r="E342" t="s">
+        <v>8</v>
+      </c>
+      <c r="F342" t="s">
+        <v>8</v>
+      </c>
+      <c r="G342" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" t="s">
+        <v>41</v>
+      </c>
+      <c r="B343" t="s">
+        <v>163</v>
+      </c>
+      <c r="C343" t="s">
+        <v>179</v>
+      </c>
+      <c r="D343" t="s">
+        <v>177</v>
+      </c>
+      <c r="E343" t="s">
+        <v>7</v>
+      </c>
+      <c r="F343" t="s">
+        <v>194</v>
+      </c>
+      <c r="G343" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" t="s">
+        <v>41</v>
+      </c>
+      <c r="B344" t="s">
+        <v>164</v>
+      </c>
+      <c r="C344" t="s">
+        <v>192</v>
+      </c>
+      <c r="D344" t="s">
         <v>180</v>
       </c>
-      <c r="G340" t="s">
+      <c r="E344" t="s">
+        <v>7</v>
+      </c>
+      <c r="F344" t="s">
+        <v>7</v>
+      </c>
+      <c r="G344" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" t="s">
+        <v>41</v>
+      </c>
+      <c r="B345" t="s">
+        <v>164</v>
+      </c>
+      <c r="C345" t="s">
+        <v>174</v>
+      </c>
+      <c r="D345" t="s">
+        <v>175</v>
+      </c>
+      <c r="E345" t="s">
+        <v>194</v>
+      </c>
+      <c r="F345" t="s">
+        <v>194</v>
+      </c>
+      <c r="G345" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" t="s">
+        <v>41</v>
+      </c>
+      <c r="B346" t="s">
+        <v>164</v>
+      </c>
+      <c r="C346" t="s">
+        <v>185</v>
+      </c>
+      <c r="D346" t="s">
+        <v>187</v>
+      </c>
+      <c r="E346" t="s">
+        <v>8</v>
+      </c>
+      <c r="F346" t="s">
+        <v>7</v>
+      </c>
+      <c r="G346" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" t="s">
+        <v>41</v>
+      </c>
+      <c r="B347" t="s">
+        <v>164</v>
+      </c>
+      <c r="C347" t="s">
+        <v>186</v>
+      </c>
+      <c r="D347" t="s">
+        <v>176</v>
+      </c>
+      <c r="E347" t="s">
+        <v>9</v>
+      </c>
+      <c r="F347" t="s">
+        <v>9</v>
+      </c>
+      <c r="G347" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" t="s">
+        <v>41</v>
+      </c>
+      <c r="B348" t="s">
+        <v>164</v>
+      </c>
+      <c r="C348" t="s">
+        <v>178</v>
+      </c>
+      <c r="D348" t="s">
+        <v>188</v>
+      </c>
+      <c r="E348" t="s">
+        <v>7</v>
+      </c>
+      <c r="F348" t="s">
+        <v>7</v>
+      </c>
+      <c r="G348" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" t="s">
+        <v>41</v>
+      </c>
+      <c r="B349" t="s">
+        <v>165</v>
+      </c>
+      <c r="C349" t="s">
+        <v>191</v>
+      </c>
+      <c r="D349" t="s">
+        <v>193</v>
+      </c>
+      <c r="E349" t="s">
+        <v>7</v>
+      </c>
+      <c r="F349" t="s">
+        <v>8</v>
+      </c>
+      <c r="G349" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" t="s">
+        <v>41</v>
+      </c>
+      <c r="B350" t="s">
+        <v>165</v>
+      </c>
+      <c r="C350" t="s">
         <v>181</v>
+      </c>
+      <c r="D350" t="s">
+        <v>190</v>
+      </c>
+      <c r="E350" t="s">
+        <v>7</v>
+      </c>
+      <c r="F350" t="s">
+        <v>7</v>
+      </c>
+      <c r="G350" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" t="s">
+        <v>42</v>
+      </c>
+      <c r="B351" t="s">
+        <v>166</v>
+      </c>
+      <c r="C351" t="s">
+        <v>175</v>
+      </c>
+      <c r="D351" t="s">
+        <v>177</v>
+      </c>
+      <c r="E351" t="s">
+        <v>194</v>
+      </c>
+      <c r="F351" t="s">
+        <v>11</v>
+      </c>
+      <c r="G351" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" t="s">
+        <v>42</v>
+      </c>
+      <c r="B352" t="s">
+        <v>167</v>
+      </c>
+      <c r="C352" t="s">
+        <v>190</v>
+      </c>
+      <c r="D352" t="s">
+        <v>183</v>
+      </c>
+      <c r="E352" t="s">
+        <v>194</v>
+      </c>
+      <c r="F352" t="s">
+        <v>8</v>
+      </c>
+      <c r="G352" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" t="s">
+        <v>42</v>
+      </c>
+      <c r="B353" t="s">
+        <v>167</v>
+      </c>
+      <c r="C353" t="s">
+        <v>186</v>
+      </c>
+      <c r="D353" t="s">
+        <v>192</v>
+      </c>
+      <c r="E353" t="s">
+        <v>11</v>
+      </c>
+      <c r="F353" t="s">
+        <v>7</v>
+      </c>
+      <c r="G353" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" t="s">
+        <v>42</v>
+      </c>
+      <c r="B354" t="s">
+        <v>168</v>
+      </c>
+      <c r="C354" t="s">
+        <v>189</v>
+      </c>
+      <c r="D354" t="s">
+        <v>174</v>
+      </c>
+      <c r="E354" t="s">
+        <v>8</v>
+      </c>
+      <c r="F354" t="s">
+        <v>194</v>
+      </c>
+      <c r="G354" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" t="s">
+        <v>42</v>
+      </c>
+      <c r="B355" t="s">
+        <v>168</v>
+      </c>
+      <c r="C355" t="s">
+        <v>176</v>
+      </c>
+      <c r="D355" t="s">
+        <v>179</v>
+      </c>
+      <c r="E355" t="s">
+        <v>8</v>
+      </c>
+      <c r="F355" t="s">
+        <v>7</v>
+      </c>
+      <c r="G355" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" t="s">
+        <v>42</v>
+      </c>
+      <c r="B356" t="s">
+        <v>168</v>
+      </c>
+      <c r="C356" t="s">
+        <v>185</v>
+      </c>
+      <c r="D356" t="s">
+        <v>182</v>
+      </c>
+      <c r="E356" t="s">
+        <v>7</v>
+      </c>
+      <c r="F356" t="s">
+        <v>8</v>
+      </c>
+      <c r="G356" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" t="s">
+        <v>42</v>
+      </c>
+      <c r="B357" t="s">
+        <v>168</v>
+      </c>
+      <c r="C357" t="s">
+        <v>188</v>
+      </c>
+      <c r="D357" t="s">
+        <v>191</v>
+      </c>
+      <c r="E357" t="s">
+        <v>7</v>
+      </c>
+      <c r="F357" t="s">
+        <v>7</v>
+      </c>
+      <c r="G357" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" t="s">
+        <v>42</v>
+      </c>
+      <c r="B358" t="s">
+        <v>168</v>
+      </c>
+      <c r="C358" t="s">
+        <v>193</v>
+      </c>
+      <c r="D358" t="s">
+        <v>178</v>
+      </c>
+      <c r="E358" t="s">
+        <v>8</v>
+      </c>
+      <c r="F358" t="s">
+        <v>7</v>
+      </c>
+      <c r="G358" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" t="s">
+        <v>42</v>
+      </c>
+      <c r="B359" t="s">
+        <v>169</v>
+      </c>
+      <c r="C359" t="s">
+        <v>180</v>
+      </c>
+      <c r="D359" t="s">
+        <v>181</v>
+      </c>
+      <c r="E359" t="s">
+        <v>194</v>
+      </c>
+      <c r="F359" t="s">
+        <v>8</v>
+      </c>
+      <c r="G359" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" t="s">
+        <v>42</v>
+      </c>
+      <c r="B360" t="s">
+        <v>169</v>
+      </c>
+      <c r="C360" t="s">
+        <v>187</v>
+      </c>
+      <c r="D360" t="s">
+        <v>184</v>
+      </c>
+      <c r="E360" t="s">
+        <v>8</v>
+      </c>
+      <c r="F360" t="s">
+        <v>7</v>
+      </c>
+      <c r="G360" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" t="s">
+        <v>43</v>
+      </c>
+      <c r="B361" t="s">
+        <v>170</v>
+      </c>
+      <c r="C361" t="s">
+        <v>187</v>
+      </c>
+      <c r="D361" t="s">
+        <v>190</v>
+      </c>
+      <c r="E361" t="s">
+        <v>8</v>
+      </c>
+      <c r="F361" t="s">
+        <v>8</v>
+      </c>
+      <c r="G361" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" t="s">
+        <v>43</v>
+      </c>
+      <c r="B362" t="s">
+        <v>171</v>
+      </c>
+      <c r="C362" t="s">
+        <v>180</v>
+      </c>
+      <c r="D362" t="s">
+        <v>193</v>
+      </c>
+      <c r="E362" t="s">
+        <v>194</v>
+      </c>
+      <c r="F362" t="s">
+        <v>8</v>
+      </c>
+      <c r="G362" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" t="s">
+        <v>43</v>
+      </c>
+      <c r="B363" t="s">
+        <v>171</v>
+      </c>
+      <c r="C363" t="s">
+        <v>182</v>
+      </c>
+      <c r="D363" t="s">
+        <v>186</v>
+      </c>
+      <c r="E363" t="s">
+        <v>9</v>
+      </c>
+      <c r="F363" t="s">
+        <v>7</v>
+      </c>
+      <c r="G363" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" t="s">
+        <v>43</v>
+      </c>
+      <c r="B364" t="s">
+        <v>172</v>
+      </c>
+      <c r="C364" t="s">
+        <v>179</v>
+      </c>
+      <c r="D364" t="s">
+        <v>192</v>
+      </c>
+      <c r="E364" t="s">
+        <v>194</v>
+      </c>
+      <c r="F364" t="s">
+        <v>8</v>
+      </c>
+      <c r="G364" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" t="s">
+        <v>43</v>
+      </c>
+      <c r="B365" t="s">
+        <v>172</v>
+      </c>
+      <c r="C365" t="s">
+        <v>184</v>
+      </c>
+      <c r="D365" t="s">
+        <v>175</v>
+      </c>
+      <c r="E365" t="s">
+        <v>194</v>
+      </c>
+      <c r="F365" t="s">
+        <v>7</v>
+      </c>
+      <c r="G365" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" t="s">
+        <v>43</v>
+      </c>
+      <c r="B366" t="s">
+        <v>172</v>
+      </c>
+      <c r="C366" t="s">
+        <v>181</v>
+      </c>
+      <c r="D366" t="s">
+        <v>174</v>
+      </c>
+      <c r="E366" t="s">
+        <v>7</v>
+      </c>
+      <c r="F366" t="s">
+        <v>7</v>
+      </c>
+      <c r="G366" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" t="s">
+        <v>43</v>
+      </c>
+      <c r="B367" t="s">
+        <v>172</v>
+      </c>
+      <c r="C367" t="s">
+        <v>177</v>
+      </c>
+      <c r="D367" t="s">
+        <v>189</v>
+      </c>
+      <c r="E367" t="s">
+        <v>7</v>
+      </c>
+      <c r="F367" t="s">
+        <v>7</v>
+      </c>
+      <c r="G367" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" t="s">
+        <v>43</v>
+      </c>
+      <c r="B368" t="s">
+        <v>172</v>
+      </c>
+      <c r="C368" t="s">
+        <v>178</v>
+      </c>
+      <c r="D368" t="s">
+        <v>176</v>
+      </c>
+      <c r="E368" t="s">
+        <v>7</v>
+      </c>
+      <c r="F368" t="s">
+        <v>194</v>
+      </c>
+      <c r="G368" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" t="s">
+        <v>43</v>
+      </c>
+      <c r="B369" t="s">
+        <v>173</v>
+      </c>
+      <c r="C369" t="s">
+        <v>191</v>
+      </c>
+      <c r="D369" t="s">
+        <v>185</v>
+      </c>
+      <c r="E369" t="s">
+        <v>7</v>
+      </c>
+      <c r="F369" t="s">
+        <v>8</v>
+      </c>
+      <c r="G369" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" t="s">
+        <v>43</v>
+      </c>
+      <c r="B370" t="s">
+        <v>173</v>
+      </c>
+      <c r="C370" t="s">
+        <v>183</v>
+      </c>
+      <c r="D370" t="s">
+        <v>188</v>
+      </c>
+      <c r="E370" t="s">
+        <v>9</v>
+      </c>
+      <c r="F370" t="s">
+        <v>9</v>
+      </c>
+      <c r="G370" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
